--- a/app/templates/Template_Angularidad.xlsx
+++ b/app/templates/Template_Angularidad.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{922821DD-BFD2-4522-9A4C-11626B890DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D68222-C4D9-4B62-A406-724B6423E0A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="635" firstSheet="15" activeTab="15" xr2:uid="{84B08A21-E3E9-471E-BCEE-1FBDE82AB453}"/>
   </bookViews>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="583">
   <si>
     <t xml:space="preserve">                 PROVIAS NACIONAL</t>
   </si>
@@ -1985,12 +1985,6 @@
   </si>
   <si>
     <t>WEB: www.geofal.com.pe   E-MAIL: laboratorio@geofal.com.pe / geofal.sac@gmail.com                                                                                                                         Av. Marañon 763, Los Olivos-Lima / Teléfono 01 522-1851</t>
-  </si>
-  <si>
-    <t>Limite Especificado</t>
-  </si>
-  <si>
-    <t>50 % Max.</t>
   </si>
   <si>
     <t>MINISTERIO DE TRANSPORTE COMUNICACIÓN VIVIENDA Y CONSTRUCCION</t>
@@ -5373,7 +5367,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1262">
+  <cellXfs count="1260">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8188,6 +8182,19 @@
     <xf numFmtId="0" fontId="62" fillId="12" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8255,15 +8262,6 @@
     <xf numFmtId="164" fontId="37" fillId="12" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8285,17 +8283,62 @@
     <xf numFmtId="164" fontId="40" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="38" fillId="12" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="12" borderId="121" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="12" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="12" borderId="122" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="12" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="12" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="12" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="43" fillId="12" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="12" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="43" fillId="12" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="40" fillId="12" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="12" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="43" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="37" fillId="12" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="171" fontId="2" fillId="12" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -8304,51 +8347,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="37" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="12" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="12" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="12" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="38" fillId="12" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="12" borderId="121" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="12" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="12" borderId="122" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="12" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="12" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="12" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="12" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="68" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -8376,48 +8374,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="46" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="50" fillId="12" borderId="99" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="50" fillId="12" borderId="98" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="126" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="121" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="127" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="99" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="98" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="128" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="129" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="50" fillId="12" borderId="99" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="50" fillId="12" borderId="98" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="20" fontId="50" fillId="12" borderId="99" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -8450,6 +8406,57 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="97" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="46" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="50" fillId="12" borderId="99" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="50" fillId="12" borderId="98" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="126" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="121" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="127" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="99" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="98" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="128" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="129" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="50" fillId="12" borderId="99" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="50" fillId="12" borderId="98" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8458,6 +8465,18 @@
     </xf>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="77" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="12" borderId="126" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8489,27 +8508,6 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="77" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="50" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8540,15 +8538,78 @@
     <xf numFmtId="0" fontId="50" fillId="12" borderId="98" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="130" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="131" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="132" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="133" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="134" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="135" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="132" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="137" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -8561,9 +8622,6 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8582,65 +8640,62 @@
     <xf numFmtId="0" fontId="25" fillId="3" borderId="130" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="131" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="132" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="133" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="134" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="135" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="130" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="145" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="151" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="142" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="145" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="147" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="146" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="149" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="142" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8672,154 +8727,97 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="144" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="145" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="146" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="145" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="151" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="142" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="147" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="149" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="142" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="12" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="12" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="12" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="12" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="12" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="12" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="12" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="12" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="72" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="83" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="72" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="72" fillId="12" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="12" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="12" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="12" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="12" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="12" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="12" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="12" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="12" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="82" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="86" fillId="12" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="12" borderId="154" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="12" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="12" borderId="65" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="72" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="72" fillId="12" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="12" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="12" borderId="154" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="12" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="12" borderId="65" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -8834,106 +8832,61 @@
     <xf numFmtId="167" fontId="59" fillId="12" borderId="41" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="12" borderId="119" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="12" borderId="112" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="12" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="12" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="118" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="12" borderId="113" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="12" borderId="101" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="20" fillId="12" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="12" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="12" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="12" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="173" fontId="62" fillId="12" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="62" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="118" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8961,21 +8914,50 @@
     <xf numFmtId="0" fontId="50" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="12" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="162" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="163" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="12" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="12" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="12" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="12" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="12" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="62" fillId="12" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="62" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="12" borderId="119" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="12" borderId="112" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="12" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="12" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="118" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9008,6 +8990,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="162" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="163" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -9052,10 +9044,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="12" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -22981,15 +22969,15 @@
       <c r="A1" s="69" t="s">
         <v>288</v>
       </c>
-      <c r="B1" s="1100" t="s">
+      <c r="B1" s="1122" t="s">
         <v>289</v>
       </c>
-      <c r="C1" s="1100"/>
-      <c r="D1" s="1100"/>
-      <c r="E1" s="1100"/>
-      <c r="F1" s="1100"/>
-      <c r="G1" s="1100"/>
-      <c r="H1" s="1100"/>
+      <c r="C1" s="1122"/>
+      <c r="D1" s="1122"/>
+      <c r="E1" s="1122"/>
+      <c r="F1" s="1122"/>
+      <c r="G1" s="1122"/>
+      <c r="H1" s="1122"/>
       <c r="I1" s="69"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -23123,29 +23111,29 @@
     </row>
     <row r="8" spans="1:17" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="69"/>
-      <c r="B8" s="1101" t="s">
+      <c r="B8" s="1123" t="s">
         <v>301</v>
       </c>
-      <c r="C8" s="1101"/>
-      <c r="D8" s="1101"/>
+      <c r="C8" s="1123"/>
+      <c r="D8" s="1123"/>
       <c r="E8" s="79" t="s">
         <v>302</v>
       </c>
       <c r="F8" s="80" t="s">
         <v>303</v>
       </c>
-      <c r="G8" s="1102" t="s">
+      <c r="G8" s="1124" t="s">
         <v>304</v>
       </c>
-      <c r="H8" s="1102"/>
+      <c r="H8" s="1124"/>
       <c r="I8" s="69"/>
       <c r="L8" s="81" t="s">
         <v>305</v>
       </c>
-      <c r="M8" s="1125" t="s">
+      <c r="M8" s="1097" t="s">
         <v>306</v>
       </c>
-      <c r="N8" s="1125"/>
+      <c r="N8" s="1097"/>
       <c r="O8" s="82" t="s">
         <v>307</v>
       </c>
@@ -23158,13 +23146,13 @@
     </row>
     <row r="9" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="69"/>
-      <c r="B9" s="1096" t="s">
+      <c r="B9" s="1119" t="s">
         <v>310</v>
       </c>
       <c r="C9" s="1098" t="s">
         <v>311</v>
       </c>
-      <c r="D9" s="1103" t="s">
+      <c r="D9" s="1099" t="s">
         <v>312</v>
       </c>
       <c r="E9" s="84" t="s">
@@ -23173,10 +23161,10 @@
       <c r="F9" s="85" t="s">
         <v>314</v>
       </c>
-      <c r="G9" s="1104" t="s">
+      <c r="G9" s="1125" t="s">
         <v>315</v>
       </c>
-      <c r="H9" s="1105"/>
+      <c r="H9" s="1126"/>
       <c r="I9" s="69"/>
       <c r="L9" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,CU&gt;=4,CC&gt;=1,CC&lt;=3),"GW","")</f>
@@ -23205,19 +23193,19 @@
     </row>
     <row r="10" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="69"/>
-      <c r="B10" s="1096"/>
+      <c r="B10" s="1119"/>
       <c r="C10" s="1098"/>
-      <c r="D10" s="1103"/>
+      <c r="D10" s="1099"/>
       <c r="E10" s="86" t="s">
         <v>316</v>
       </c>
       <c r="F10" s="87" t="s">
         <v>317</v>
       </c>
-      <c r="G10" s="1108" t="s">
+      <c r="G10" s="1129" t="s">
         <v>318</v>
       </c>
-      <c r="H10" s="1109"/>
+      <c r="H10" s="1130"/>
       <c r="I10" s="69"/>
       <c r="L10" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,OR(CU&lt;4,CC&lt;1,CC&gt;3)),"GP","")</f>
@@ -23242,9 +23230,9 @@
     </row>
     <row r="11" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="69"/>
-      <c r="B11" s="1096"/>
+      <c r="B11" s="1119"/>
       <c r="C11" s="1098"/>
-      <c r="D11" s="1103" t="s">
+      <c r="D11" s="1099" t="s">
         <v>319</v>
       </c>
       <c r="E11" s="86" t="s">
@@ -23256,7 +23244,7 @@
       <c r="G11" s="89" t="s">
         <v>322</v>
       </c>
-      <c r="H11" s="1106" t="s">
+      <c r="H11" s="1127" t="s">
         <v>323</v>
       </c>
       <c r="I11" s="69"/>
@@ -23275,9 +23263,9 @@
     </row>
     <row r="12" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="69"/>
-      <c r="B12" s="1096"/>
-      <c r="C12" s="1099"/>
-      <c r="D12" s="1103"/>
+      <c r="B12" s="1119"/>
+      <c r="C12" s="1121"/>
+      <c r="D12" s="1099"/>
       <c r="E12" s="90" t="s">
         <v>324</v>
       </c>
@@ -23287,7 +23275,7 @@
       <c r="G12" s="89" t="s">
         <v>326</v>
       </c>
-      <c r="H12" s="1107"/>
+      <c r="H12" s="1128"/>
       <c r="I12" s="69"/>
       <c r="L12" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"GC","")</f>
@@ -23300,11 +23288,11 @@
     </row>
     <row r="13" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="69"/>
-      <c r="B13" s="1096"/>
+      <c r="B13" s="1119"/>
       <c r="C13" s="1098" t="s">
         <v>327</v>
       </c>
-      <c r="D13" s="1103" t="s">
+      <c r="D13" s="1099" t="s">
         <v>328</v>
       </c>
       <c r="E13" s="91" t="s">
@@ -23313,10 +23301,10 @@
       <c r="F13" s="92" t="s">
         <v>330</v>
       </c>
-      <c r="G13" s="1126" t="s">
+      <c r="G13" s="1100" t="s">
         <v>331</v>
       </c>
-      <c r="H13" s="1127"/>
+      <c r="H13" s="1101"/>
       <c r="I13" s="69"/>
       <c r="L13" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,CU&gt;=6,CC&gt;=1,CC&lt;=3),"SW","")</f>
@@ -23341,19 +23329,19 @@
     </row>
     <row r="14" spans="1:17" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="69"/>
-      <c r="B14" s="1096"/>
+      <c r="B14" s="1119"/>
       <c r="C14" s="1098"/>
-      <c r="D14" s="1103"/>
+      <c r="D14" s="1099"/>
       <c r="E14" s="91" t="s">
         <v>332</v>
       </c>
       <c r="F14" s="92" t="s">
         <v>333</v>
       </c>
-      <c r="G14" s="1126" t="s">
+      <c r="G14" s="1100" t="s">
         <v>334</v>
       </c>
-      <c r="H14" s="1127"/>
+      <c r="H14" s="1101"/>
       <c r="I14" s="69"/>
       <c r="L14" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,OR(CU&lt;6,CC&lt;1,CC&gt;3)),"SP","")</f>
@@ -23378,9 +23366,9 @@
     </row>
     <row r="15" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="69"/>
-      <c r="B15" s="1096"/>
+      <c r="B15" s="1119"/>
       <c r="C15" s="1098"/>
-      <c r="D15" s="1103" t="s">
+      <c r="D15" s="1099" t="s">
         <v>335</v>
       </c>
       <c r="E15" s="91" t="s">
@@ -23392,7 +23380,7 @@
       <c r="G15" s="94" t="s">
         <v>338</v>
       </c>
-      <c r="H15" s="1128" t="s">
+      <c r="H15" s="1102" t="s">
         <v>339</v>
       </c>
       <c r="I15" s="69"/>
@@ -23411,9 +23399,9 @@
     </row>
     <row r="16" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="69"/>
-      <c r="B16" s="1097"/>
+      <c r="B16" s="1120"/>
       <c r="C16" s="1098"/>
-      <c r="D16" s="1103"/>
+      <c r="D16" s="1099"/>
       <c r="E16" s="95" t="s">
         <v>340</v>
       </c>
@@ -23423,7 +23411,7 @@
       <c r="G16" s="92" t="s">
         <v>342</v>
       </c>
-      <c r="H16" s="1129"/>
+      <c r="H16" s="1103"/>
       <c r="I16" s="69"/>
       <c r="L16" t="str">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"SC","")</f>
@@ -23436,23 +23424,23 @@
     </row>
     <row r="17" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="69"/>
-      <c r="B17" s="1110" t="s">
+      <c r="B17" s="1104" t="s">
         <v>343</v>
       </c>
-      <c r="C17" s="1113" t="s">
+      <c r="C17" s="1107" t="s">
         <v>344</v>
       </c>
-      <c r="D17" s="1114"/>
+      <c r="D17" s="1108"/>
       <c r="E17" s="96" t="s">
         <v>345</v>
       </c>
       <c r="F17" s="97" t="s">
         <v>346</v>
       </c>
-      <c r="G17" s="1119" t="s">
+      <c r="G17" s="1113" t="s">
         <v>347</v>
       </c>
-      <c r="H17" s="1120"/>
+      <c r="H17" s="1114"/>
       <c r="I17" s="69"/>
       <c r="L17" t="str">
         <f>IF(AND(N_200&gt;=50,Ll&lt;50,OR(IP&lt;4,AND(IP&lt;0.73*(Ll-20),IP&lt;10))),"ML","")</f>
@@ -23465,17 +23453,17 @@
     </row>
     <row r="18" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="69"/>
-      <c r="B18" s="1111"/>
-      <c r="C18" s="1115"/>
-      <c r="D18" s="1116"/>
+      <c r="B18" s="1105"/>
+      <c r="C18" s="1109"/>
+      <c r="D18" s="1110"/>
       <c r="E18" s="96" t="s">
         <v>348</v>
       </c>
       <c r="F18" s="97" t="s">
         <v>349</v>
       </c>
-      <c r="G18" s="1121"/>
-      <c r="H18" s="1122"/>
+      <c r="G18" s="1115"/>
+      <c r="H18" s="1116"/>
       <c r="I18" s="69"/>
       <c r="L18" t="str">
         <f>IF(AND(N_200&gt;=50,Ll&lt;50,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"CL","")</f>
@@ -23488,9 +23476,9 @@
     </row>
     <row r="19" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="69"/>
-      <c r="B19" s="1111"/>
-      <c r="C19" s="1117"/>
-      <c r="D19" s="1118"/>
+      <c r="B19" s="1105"/>
+      <c r="C19" s="1111"/>
+      <c r="D19" s="1112"/>
       <c r="E19" s="96" t="s">
         <v>350</v>
       </c>
@@ -23511,11 +23499,11 @@
     </row>
     <row r="20" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="69"/>
-      <c r="B20" s="1111"/>
-      <c r="C20" s="1115" t="s">
+      <c r="B20" s="1105"/>
+      <c r="C20" s="1109" t="s">
         <v>352</v>
       </c>
-      <c r="D20" s="1123"/>
+      <c r="D20" s="1117"/>
       <c r="E20" s="100" t="s">
         <v>353</v>
       </c>
@@ -23536,9 +23524,9 @@
     </row>
     <row r="21" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="69"/>
-      <c r="B21" s="1111"/>
-      <c r="C21" s="1115"/>
-      <c r="D21" s="1123"/>
+      <c r="B21" s="1105"/>
+      <c r="C21" s="1109"/>
+      <c r="D21" s="1117"/>
       <c r="E21" s="100" t="s">
         <v>355</v>
       </c>
@@ -23559,9 +23547,9 @@
     </row>
     <row r="22" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="69"/>
-      <c r="B22" s="1111"/>
-      <c r="C22" s="1117"/>
-      <c r="D22" s="1124"/>
+      <c r="B22" s="1105"/>
+      <c r="C22" s="1111"/>
+      <c r="D22" s="1118"/>
       <c r="E22" s="102" t="s">
         <v>357</v>
       </c>
@@ -23582,11 +23570,11 @@
     </row>
     <row r="23" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="69"/>
-      <c r="B23" s="1111"/>
-      <c r="C23" s="1113" t="s">
+      <c r="B23" s="1105"/>
+      <c r="C23" s="1107" t="s">
         <v>359</v>
       </c>
-      <c r="D23" s="1114"/>
+      <c r="D23" s="1108"/>
       <c r="E23" s="103" t="s">
         <v>360</v>
       </c>
@@ -23607,7 +23595,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="69"/>
-      <c r="B24" s="1112"/>
+      <c r="B24" s="1106"/>
       <c r="C24" s="105"/>
       <c r="D24" s="106"/>
       <c r="E24" s="107"/>
@@ -23710,19 +23698,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="C13:C16"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="B17:B24"/>
-    <mergeCell ref="C17:D19"/>
-    <mergeCell ref="G17:H18"/>
-    <mergeCell ref="C20:D22"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="B9:B16"/>
     <mergeCell ref="C9:C12"/>
     <mergeCell ref="B1:H1"/>
@@ -23732,6 +23707,19 @@
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="H11:H12"/>
     <mergeCell ref="G10:H10"/>
+    <mergeCell ref="B17:B24"/>
+    <mergeCell ref="C17:D19"/>
+    <mergeCell ref="G17:H18"/>
+    <mergeCell ref="C20:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="C13:C16"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="H15:H16"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
@@ -23809,71 +23797,71 @@
     </row>
     <row r="4" spans="1:16" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="1130" t="s">
+      <c r="B4" s="1150" t="s">
         <v>362</v>
       </c>
-      <c r="C4" s="1131"/>
-      <c r="D4" s="1132" t="s">
+      <c r="C4" s="1151"/>
+      <c r="D4" s="1152" t="s">
         <v>363</v>
       </c>
-      <c r="E4" s="1132"/>
-      <c r="F4" s="1132"/>
-      <c r="G4" s="1132"/>
-      <c r="H4" s="1132"/>
-      <c r="I4" s="1132"/>
-      <c r="J4" s="1132"/>
-      <c r="K4" s="1133" t="s">
+      <c r="E4" s="1152"/>
+      <c r="F4" s="1152"/>
+      <c r="G4" s="1152"/>
+      <c r="H4" s="1152"/>
+      <c r="I4" s="1152"/>
+      <c r="J4" s="1152"/>
+      <c r="K4" s="1153" t="s">
         <v>364</v>
       </c>
-      <c r="L4" s="1134"/>
-      <c r="M4" s="1134"/>
-      <c r="N4" s="1134"/>
-      <c r="O4" s="1135"/>
+      <c r="L4" s="1154"/>
+      <c r="M4" s="1154"/>
+      <c r="N4" s="1154"/>
+      <c r="O4" s="1155"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
-      <c r="B5" s="1136" t="s">
+      <c r="B5" s="1156" t="s">
         <v>365</v>
       </c>
-      <c r="C5" s="1137"/>
-      <c r="D5" s="1140" t="s">
+      <c r="C5" s="1157"/>
+      <c r="D5" s="1141" t="s">
         <v>366</v>
       </c>
-      <c r="E5" s="1141"/>
-      <c r="F5" s="1150" t="s">
+      <c r="E5" s="1143"/>
+      <c r="F5" s="1139" t="s">
         <v>367</v>
       </c>
-      <c r="G5" s="1140" t="s">
+      <c r="G5" s="1141" t="s">
         <v>368</v>
       </c>
-      <c r="H5" s="1152"/>
-      <c r="I5" s="1152"/>
-      <c r="J5" s="1141"/>
-      <c r="K5" s="1153" t="s">
+      <c r="H5" s="1142"/>
+      <c r="I5" s="1142"/>
+      <c r="J5" s="1143"/>
+      <c r="K5" s="1144" t="s">
         <v>369</v>
       </c>
-      <c r="L5" s="1155" t="s">
+      <c r="L5" s="1146" t="s">
         <v>370</v>
       </c>
-      <c r="M5" s="1157" t="s">
+      <c r="M5" s="1148" t="s">
         <v>371</v>
       </c>
-      <c r="N5" s="1144" t="s">
+      <c r="N5" s="1133" t="s">
         <v>372</v>
       </c>
-      <c r="O5" s="1145"/>
+      <c r="O5" s="1134"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
-      <c r="B6" s="1138"/>
-      <c r="C6" s="1139"/>
+      <c r="B6" s="1158"/>
+      <c r="C6" s="1159"/>
       <c r="D6" s="4" t="s">
         <v>373</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="F6" s="1151"/>
+      <c r="F6" s="1140"/>
       <c r="G6" s="4" t="s">
         <v>375</v>
       </c>
@@ -23886,9 +23874,9 @@
       <c r="J6" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="K6" s="1154"/>
-      <c r="L6" s="1156"/>
-      <c r="M6" s="1158"/>
+      <c r="K6" s="1145"/>
+      <c r="L6" s="1147"/>
+      <c r="M6" s="1149"/>
       <c r="N6" s="8" t="s">
         <v>379</v>
       </c>
@@ -24288,21 +24276,21 @@
         <f>+D38</f>
         <v>0</v>
       </c>
-      <c r="D23" s="1146">
+      <c r="D23" s="1135">
         <v>0</v>
       </c>
-      <c r="E23" s="1147"/>
+      <c r="E23" s="1136"/>
       <c r="F23" s="1">
         <v>0</v>
       </c>
-      <c r="G23" s="1146">
+      <c r="G23" s="1135">
         <v>0</v>
       </c>
-      <c r="H23" s="1148"/>
-      <c r="I23" s="1149" t="s">
+      <c r="H23" s="1137"/>
+      <c r="I23" s="1138" t="s">
         <v>407</v>
       </c>
-      <c r="J23" s="1147"/>
+      <c r="J23" s="1136"/>
       <c r="K23" s="60" t="s">
         <v>408</v>
       </c>
@@ -24365,11 +24353,11 @@
       <c r="G26" s="65"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
-      <c r="J26" s="1142" t="str">
+      <c r="J26" s="1131" t="str">
         <f>+D31&amp;" "&amp;F38</f>
         <v>A-1-a (0)</v>
       </c>
-      <c r="K26" s="1143"/>
+      <c r="K26" s="1132"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -24589,6 +24577,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="K4:O4"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="D5:E5"/>
     <mergeCell ref="J26:K26"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="D23:E23"/>
@@ -24599,11 +24592,6 @@
     <mergeCell ref="K5:K6"/>
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="M5:M6"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:J4"/>
-    <mergeCell ref="K4:O4"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="D5:E5"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -24663,13 +24651,13 @@
         <f>100-I1</f>
         <v>100</v>
       </c>
-      <c r="L1" s="1160" t="s">
+      <c r="L1" s="1161" t="s">
         <v>413</v>
       </c>
-      <c r="M1" s="1160"/>
-      <c r="N1" s="1160"/>
-      <c r="O1" s="1160"/>
-      <c r="P1" s="1160"/>
+      <c r="M1" s="1161"/>
+      <c r="N1" s="1161"/>
+      <c r="O1" s="1161"/>
+      <c r="P1" s="1161"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="119">
@@ -24713,10 +24701,10 @@
       <c r="M2" s="133" t="s">
         <v>415</v>
       </c>
-      <c r="N2" s="1159" t="s">
+      <c r="N2" s="1160" t="s">
         <v>416</v>
       </c>
-      <c r="O2" s="1159"/>
+      <c r="O2" s="1160"/>
       <c r="P2" s="133" t="s">
         <v>417</v>
       </c>
@@ -26622,12 +26610,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" s="380" customFormat="1" ht="11.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1161" t="s">
+      <c r="A1" s="1176" t="s">
         <v>418</v>
       </c>
-      <c r="B1" s="1162"/>
-      <c r="C1" s="1162"/>
-      <c r="D1" s="1163"/>
+      <c r="B1" s="1177"/>
+      <c r="C1" s="1177"/>
+      <c r="D1" s="1178"/>
       <c r="E1" s="388"/>
       <c r="F1" s="388"/>
       <c r="G1" s="388"/>
@@ -26649,10 +26637,10 @@
       <c r="W1" s="406"/>
     </row>
     <row r="2" spans="1:23" s="380" customFormat="1" ht="11.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1164"/>
-      <c r="B2" s="1004"/>
-      <c r="C2" s="1004"/>
-      <c r="D2" s="1165"/>
+      <c r="A2" s="1179"/>
+      <c r="B2" s="983"/>
+      <c r="C2" s="983"/>
+      <c r="D2" s="1180"/>
       <c r="E2" s="388"/>
       <c r="F2" s="388"/>
       <c r="G2" s="388"/>
@@ -26674,10 +26662,10 @@
       <c r="W2" s="406"/>
     </row>
     <row r="3" spans="1:23" s="380" customFormat="1" ht="11.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1164"/>
-      <c r="B3" s="1004"/>
-      <c r="C3" s="1004"/>
-      <c r="D3" s="1165"/>
+      <c r="A3" s="1179"/>
+      <c r="B3" s="983"/>
+      <c r="C3" s="983"/>
+      <c r="D3" s="1180"/>
       <c r="E3" s="388"/>
       <c r="F3" s="388"/>
       <c r="G3" s="388"/>
@@ -26699,10 +26687,10 @@
       <c r="W3" s="406"/>
     </row>
     <row r="4" spans="1:23" s="380" customFormat="1" ht="11.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1166"/>
-      <c r="B4" s="1167"/>
-      <c r="C4" s="1167"/>
-      <c r="D4" s="1168"/>
+      <c r="A4" s="1181"/>
+      <c r="B4" s="1182"/>
+      <c r="C4" s="1182"/>
+      <c r="D4" s="1183"/>
       <c r="E4" s="388"/>
       <c r="F4" s="388"/>
       <c r="G4" s="388"/>
@@ -26724,21 +26712,21 @@
       <c r="W4" s="406"/>
     </row>
     <row r="5" spans="1:23" s="380" customFormat="1" ht="11.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1173"/>
-      <c r="B5" s="1173"/>
-      <c r="C5" s="1173"/>
-      <c r="D5" s="1173"/>
-      <c r="E5" s="1173"/>
-      <c r="F5" s="1173"/>
-      <c r="G5" s="1173"/>
-      <c r="H5" s="1173"/>
-      <c r="I5" s="1173"/>
-      <c r="J5" s="1173"/>
-      <c r="K5" s="1173"/>
-      <c r="L5" s="1173"/>
-      <c r="M5" s="1173"/>
-      <c r="N5" s="1173"/>
-      <c r="O5" s="1173"/>
+      <c r="A5" s="1171"/>
+      <c r="B5" s="1171"/>
+      <c r="C5" s="1171"/>
+      <c r="D5" s="1171"/>
+      <c r="E5" s="1171"/>
+      <c r="F5" s="1171"/>
+      <c r="G5" s="1171"/>
+      <c r="H5" s="1171"/>
+      <c r="I5" s="1171"/>
+      <c r="J5" s="1171"/>
+      <c r="K5" s="1171"/>
+      <c r="L5" s="1171"/>
+      <c r="M5" s="1171"/>
+      <c r="N5" s="1171"/>
+      <c r="O5" s="1171"/>
       <c r="P5" s="387"/>
       <c r="Q5" s="387"/>
       <c r="R5" s="406"/>
@@ -26749,23 +26737,23 @@
       <c r="W5" s="406"/>
     </row>
     <row r="6" spans="1:23" s="380" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1175" t="s">
+      <c r="A6" s="1173" t="s">
         <v>419</v>
       </c>
-      <c r="B6" s="1176"/>
-      <c r="C6" s="1176"/>
-      <c r="D6" s="1176"/>
-      <c r="E6" s="1176"/>
-      <c r="F6" s="1176"/>
-      <c r="G6" s="1176"/>
-      <c r="H6" s="1176"/>
-      <c r="I6" s="1176"/>
-      <c r="J6" s="1176"/>
-      <c r="K6" s="1176"/>
-      <c r="L6" s="1176"/>
-      <c r="M6" s="1176"/>
-      <c r="N6" s="1176"/>
-      <c r="O6" s="1176"/>
+      <c r="B6" s="1174"/>
+      <c r="C6" s="1174"/>
+      <c r="D6" s="1174"/>
+      <c r="E6" s="1174"/>
+      <c r="F6" s="1174"/>
+      <c r="G6" s="1174"/>
+      <c r="H6" s="1174"/>
+      <c r="I6" s="1174"/>
+      <c r="J6" s="1174"/>
+      <c r="K6" s="1174"/>
+      <c r="L6" s="1174"/>
+      <c r="M6" s="1174"/>
+      <c r="N6" s="1174"/>
+      <c r="O6" s="1174"/>
       <c r="P6" s="406"/>
       <c r="Q6" s="406"/>
       <c r="R6" s="406"/>
@@ -26921,11 +26909,11 @@
       <c r="C12" s="145" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="1177" t="e">
+      <c r="D12" s="1175" t="e">
         <f>Datos!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E12" s="1177"/>
+      <c r="E12" s="1175"/>
       <c r="F12" s="351"/>
       <c r="G12" s="351"/>
       <c r="H12" s="349"/>
@@ -26933,8 +26921,8 @@
       <c r="J12" s="349"/>
       <c r="K12" s="391"/>
       <c r="L12" s="392"/>
-      <c r="M12" s="1174"/>
-      <c r="N12" s="1174"/>
+      <c r="M12" s="1172"/>
+      <c r="N12" s="1172"/>
       <c r="O12" s="351"/>
       <c r="P12" s="407"/>
       <c r="Q12" s="407"/>
@@ -26998,10 +26986,10 @@
       <c r="W14" s="407"/>
     </row>
     <row r="15" spans="1:23" s="381" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="1171" t="s">
+      <c r="A15" s="1184" t="s">
         <v>424</v>
       </c>
-      <c r="B15" s="1171" t="s">
+      <c r="B15" s="1184" t="s">
         <v>425</v>
       </c>
       <c r="C15" s="1169" t="s">
@@ -27037,40 +27025,40 @@
       <c r="M15" s="1169" t="s">
         <v>435</v>
       </c>
-      <c r="N15" s="1172" t="s">
+      <c r="N15" s="1170" t="s">
         <v>436</v>
       </c>
-      <c r="O15" s="1172" t="s">
+      <c r="O15" s="1170" t="s">
         <v>437</v>
       </c>
-      <c r="P15" s="1180" t="s">
+      <c r="P15" s="1164" t="s">
         <v>438</v>
       </c>
-      <c r="Q15" s="1178" t="s">
+      <c r="Q15" s="1162" t="s">
         <v>439</v>
       </c>
-      <c r="R15" s="1178" t="s">
+      <c r="R15" s="1162" t="s">
         <v>440</v>
       </c>
-      <c r="S15" s="1178" t="s">
+      <c r="S15" s="1162" t="s">
         <v>441</v>
       </c>
-      <c r="T15" s="1178" t="s">
+      <c r="T15" s="1162" t="s">
         <v>442</v>
       </c>
-      <c r="U15" s="1178" t="s">
+      <c r="U15" s="1162" t="s">
         <v>443</v>
       </c>
-      <c r="V15" s="1178" t="s">
+      <c r="V15" s="1162" t="s">
         <v>444</v>
       </c>
-      <c r="W15" s="1182" t="s">
+      <c r="W15" s="1166" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="16" spans="1:23" s="381" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="1171"/>
-      <c r="B16" s="1171"/>
+      <c r="A16" s="1184"/>
+      <c r="B16" s="1184"/>
       <c r="C16" s="1169"/>
       <c r="D16" s="1169"/>
       <c r="E16" s="1169"/>
@@ -27084,16 +27072,16 @@
       <c r="K16" s="1169"/>
       <c r="L16" s="1169"/>
       <c r="M16" s="1169"/>
-      <c r="N16" s="1172"/>
-      <c r="O16" s="1172"/>
-      <c r="P16" s="1181"/>
-      <c r="Q16" s="1179"/>
-      <c r="R16" s="1179"/>
-      <c r="S16" s="1179"/>
-      <c r="T16" s="1179"/>
-      <c r="U16" s="1179"/>
-      <c r="V16" s="1179"/>
-      <c r="W16" s="1183"/>
+      <c r="N16" s="1170"/>
+      <c r="O16" s="1170"/>
+      <c r="P16" s="1165"/>
+      <c r="Q16" s="1163"/>
+      <c r="R16" s="1163"/>
+      <c r="S16" s="1163"/>
+      <c r="T16" s="1163"/>
+      <c r="U16" s="1163"/>
+      <c r="V16" s="1163"/>
+      <c r="W16" s="1167"/>
     </row>
     <row r="17" spans="1:23" s="383" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="396">
@@ -28191,16 +28179,16 @@
       <c r="A39" s="144"/>
       <c r="B39" s="144"/>
       <c r="C39" s="144"/>
-      <c r="D39" s="1170"/>
-      <c r="E39" s="1170"/>
+      <c r="D39" s="1168"/>
+      <c r="E39" s="1168"/>
       <c r="F39" s="144"/>
       <c r="G39" s="144"/>
-      <c r="H39" s="1170"/>
-      <c r="I39" s="1170"/>
+      <c r="H39" s="1168"/>
+      <c r="I39" s="1168"/>
       <c r="J39" s="144"/>
       <c r="K39" s="144"/>
-      <c r="L39" s="1170"/>
-      <c r="M39" s="1170"/>
+      <c r="L39" s="1168"/>
+      <c r="M39" s="1168"/>
       <c r="N39" s="144"/>
       <c r="O39" s="144"/>
     </row>
@@ -28251,14 +28239,16 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="R15:R16"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="P15:P16"/>
-    <mergeCell ref="W15:W16"/>
-    <mergeCell ref="V15:V16"/>
-    <mergeCell ref="U15:U16"/>
-    <mergeCell ref="T15:T16"/>
-    <mergeCell ref="S15:S16"/>
+    <mergeCell ref="A1:D4"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
     <mergeCell ref="L39:M39"/>
     <mergeCell ref="M15:M16"/>
     <mergeCell ref="N15:N16"/>
@@ -28271,16 +28261,14 @@
     <mergeCell ref="L15:L16"/>
     <mergeCell ref="A6:O6"/>
     <mergeCell ref="D12:E12"/>
-    <mergeCell ref="A1:D4"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="R15:R16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="W15:W16"/>
+    <mergeCell ref="V15:V16"/>
+    <mergeCell ref="U15:U16"/>
+    <mergeCell ref="T15:T16"/>
+    <mergeCell ref="S15:S16"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -28331,20 +28319,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="11.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1184" t="s">
+      <c r="A1" s="1185" t="s">
         <v>418</v>
       </c>
       <c r="D1" s="159"/>
       <c r="E1" s="159"/>
     </row>
     <row r="2" spans="1:5" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1185"/>
+      <c r="A2" s="1186"/>
     </row>
     <row r="3" spans="1:5" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1185"/>
+      <c r="A3" s="1186"/>
     </row>
     <row r="4" spans="1:5" ht="11.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1186"/>
+      <c r="A4" s="1187"/>
       <c r="B4" s="168"/>
       <c r="C4" s="169"/>
       <c r="D4" s="168"/>
@@ -28355,12 +28343,12 @@
       <c r="B5" s="312"/>
     </row>
     <row r="6" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1187" t="s">
+      <c r="A6" s="1188" t="s">
         <v>465</v>
       </c>
-      <c r="B6" s="1187"/>
-      <c r="C6" s="1187"/>
-      <c r="D6" s="1187"/>
+      <c r="B6" s="1188"/>
+      <c r="C6" s="1188"/>
+      <c r="D6" s="1188"/>
     </row>
     <row r="7" spans="1:5" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="211"/>
@@ -28369,10 +28357,10 @@
       <c r="D7" s="220"/>
     </row>
     <row r="8" spans="1:5" ht="13.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1189"/>
-      <c r="B8" s="1189"/>
-      <c r="C8" s="1189"/>
-      <c r="D8" s="1189"/>
+      <c r="A8" s="1190"/>
+      <c r="B8" s="1190"/>
+      <c r="C8" s="1190"/>
+      <c r="D8" s="1190"/>
     </row>
     <row r="9" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="314"/>
@@ -28481,12 +28469,12 @@
       <c r="D20" s="327"/>
     </row>
     <row r="21" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1190" t="s">
+      <c r="A21" s="1191" t="s">
         <v>466</v>
       </c>
-      <c r="B21" s="1190"/>
-      <c r="C21" s="1190"/>
-      <c r="D21" s="1190"/>
+      <c r="B21" s="1191"/>
+      <c r="C21" s="1191"/>
+      <c r="D21" s="1191"/>
     </row>
     <row r="22" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:4" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -28564,12 +28552,12 @@
       <c r="A30" s="328" t="s">
         <v>474</v>
       </c>
-      <c r="B30" s="1191">
+      <c r="B30" s="1192">
         <f>AVERAGE(B29:D29)/100</f>
         <v>0.23571428571428577</v>
       </c>
-      <c r="C30" s="1192"/>
-      <c r="D30" s="1193"/>
+      <c r="C30" s="1193"/>
+      <c r="D30" s="1194"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B31" s="140"/>
@@ -28598,8 +28586,8 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="340"/>
-      <c r="B35" s="1188"/>
-      <c r="C35" s="1188"/>
+      <c r="B35" s="1189"/>
+      <c r="C35" s="1189"/>
       <c r="D35" s="341"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -28694,69 +28682,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="1213"/>
-      <c r="C1" s="1214"/>
-      <c r="D1" s="1214"/>
-      <c r="E1" s="1214"/>
-      <c r="F1" s="1214"/>
-      <c r="G1" s="1214"/>
-      <c r="H1" s="1214"/>
-      <c r="I1" s="1214"/>
-      <c r="J1" s="1214"/>
-      <c r="K1" s="1214"/>
-      <c r="L1" s="1215"/>
+      <c r="B1" s="1195"/>
+      <c r="C1" s="1196"/>
+      <c r="D1" s="1196"/>
+      <c r="E1" s="1196"/>
+      <c r="F1" s="1196"/>
+      <c r="G1" s="1196"/>
+      <c r="H1" s="1196"/>
+      <c r="I1" s="1196"/>
+      <c r="J1" s="1196"/>
+      <c r="K1" s="1196"/>
+      <c r="L1" s="1197"/>
     </row>
     <row r="2" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="1216"/>
-      <c r="C2" s="1217"/>
-      <c r="D2" s="1217"/>
-      <c r="E2" s="1217"/>
-      <c r="F2" s="1217"/>
-      <c r="G2" s="1217"/>
-      <c r="H2" s="1217"/>
-      <c r="I2" s="1217"/>
-      <c r="J2" s="1217"/>
-      <c r="K2" s="1217"/>
-      <c r="L2" s="1218"/>
+      <c r="B2" s="1198"/>
+      <c r="C2" s="1199"/>
+      <c r="D2" s="1199"/>
+      <c r="E2" s="1199"/>
+      <c r="F2" s="1199"/>
+      <c r="G2" s="1199"/>
+      <c r="H2" s="1199"/>
+      <c r="I2" s="1199"/>
+      <c r="J2" s="1199"/>
+      <c r="K2" s="1199"/>
+      <c r="L2" s="1200"/>
     </row>
     <row r="3" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="1216"/>
-      <c r="C3" s="1217"/>
-      <c r="D3" s="1217"/>
-      <c r="E3" s="1217"/>
-      <c r="F3" s="1217"/>
-      <c r="G3" s="1217"/>
-      <c r="H3" s="1217"/>
-      <c r="I3" s="1217"/>
-      <c r="J3" s="1217"/>
-      <c r="K3" s="1217"/>
-      <c r="L3" s="1218"/>
+      <c r="B3" s="1198"/>
+      <c r="C3" s="1199"/>
+      <c r="D3" s="1199"/>
+      <c r="E3" s="1199"/>
+      <c r="F3" s="1199"/>
+      <c r="G3" s="1199"/>
+      <c r="H3" s="1199"/>
+      <c r="I3" s="1199"/>
+      <c r="J3" s="1199"/>
+      <c r="K3" s="1199"/>
+      <c r="L3" s="1200"/>
     </row>
     <row r="4" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="1216"/>
-      <c r="C4" s="1217"/>
-      <c r="D4" s="1217"/>
-      <c r="E4" s="1217"/>
-      <c r="F4" s="1217"/>
-      <c r="G4" s="1217"/>
-      <c r="H4" s="1217"/>
-      <c r="I4" s="1217"/>
-      <c r="J4" s="1217"/>
-      <c r="K4" s="1217"/>
-      <c r="L4" s="1218"/>
+      <c r="B4" s="1198"/>
+      <c r="C4" s="1199"/>
+      <c r="D4" s="1199"/>
+      <c r="E4" s="1199"/>
+      <c r="F4" s="1199"/>
+      <c r="G4" s="1199"/>
+      <c r="H4" s="1199"/>
+      <c r="I4" s="1199"/>
+      <c r="J4" s="1199"/>
+      <c r="K4" s="1199"/>
+      <c r="L4" s="1200"/>
     </row>
     <row r="5" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="1219"/>
-      <c r="C5" s="1220"/>
-      <c r="D5" s="1220"/>
-      <c r="E5" s="1220"/>
-      <c r="F5" s="1220"/>
-      <c r="G5" s="1220"/>
-      <c r="H5" s="1220"/>
-      <c r="I5" s="1220"/>
-      <c r="J5" s="1220"/>
-      <c r="K5" s="1220"/>
-      <c r="L5" s="1221"/>
+      <c r="B5" s="1201"/>
+      <c r="C5" s="1202"/>
+      <c r="D5" s="1202"/>
+      <c r="E5" s="1202"/>
+      <c r="F5" s="1202"/>
+      <c r="G5" s="1202"/>
+      <c r="H5" s="1202"/>
+      <c r="I5" s="1202"/>
+      <c r="J5" s="1202"/>
+      <c r="K5" s="1202"/>
+      <c r="L5" s="1203"/>
     </row>
     <row r="6" spans="2:12" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B6" s="813"/>
@@ -28782,35 +28770,35 @@
       <c r="J7" s="815"/>
     </row>
     <row r="8" spans="2:12" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="B8" s="1228" t="s">
+      <c r="B8" s="1214" t="s">
         <v>476</v>
       </c>
-      <c r="C8" s="1228"/>
-      <c r="D8" s="1228"/>
-      <c r="E8" s="1228"/>
-      <c r="F8" s="1228"/>
-      <c r="G8" s="1228"/>
-      <c r="H8" s="1228"/>
-      <c r="I8" s="1228"/>
-      <c r="J8" s="1228"/>
-      <c r="K8" s="1228"/>
-      <c r="L8" s="1228"/>
+      <c r="C8" s="1214"/>
+      <c r="D8" s="1214"/>
+      <c r="E8" s="1214"/>
+      <c r="F8" s="1214"/>
+      <c r="G8" s="1214"/>
+      <c r="H8" s="1214"/>
+      <c r="I8" s="1214"/>
+      <c r="J8" s="1214"/>
+      <c r="K8" s="1214"/>
+      <c r="L8" s="1214"/>
     </row>
     <row r="9" spans="2:12" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="B9" s="1229">
+      <c r="B9" s="1215">
         <f>L13</f>
         <v>2</v>
       </c>
-      <c r="C9" s="1229"/>
-      <c r="D9" s="1229"/>
-      <c r="E9" s="1229"/>
-      <c r="F9" s="1229"/>
-      <c r="G9" s="1229"/>
-      <c r="H9" s="1229"/>
-      <c r="I9" s="1229"/>
-      <c r="J9" s="1229"/>
-      <c r="K9" s="1229"/>
-      <c r="L9" s="1229"/>
+      <c r="C9" s="1215"/>
+      <c r="D9" s="1215"/>
+      <c r="E9" s="1215"/>
+      <c r="F9" s="1215"/>
+      <c r="G9" s="1215"/>
+      <c r="H9" s="1215"/>
+      <c r="I9" s="1215"/>
+      <c r="J9" s="1215"/>
+      <c r="K9" s="1215"/>
+      <c r="L9" s="1215"/>
     </row>
     <row r="10" spans="2:12" ht="13.8" x14ac:dyDescent="0.25">
       <c r="B10" s="806"/>
@@ -28904,47 +28892,47 @@
       <c r="C14" s="134"/>
     </row>
     <row r="15" spans="2:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="1230" t="s">
+      <c r="B15" s="1216" t="s">
         <v>487</v>
       </c>
-      <c r="C15" s="1231"/>
-      <c r="D15" s="1231"/>
-      <c r="E15" s="1231"/>
-      <c r="F15" s="1231"/>
-      <c r="G15" s="1231"/>
-      <c r="H15" s="1231"/>
-      <c r="I15" s="1231"/>
-      <c r="J15" s="1231"/>
-      <c r="K15" s="1231"/>
-      <c r="L15" s="1231"/>
+      <c r="C15" s="1217"/>
+      <c r="D15" s="1217"/>
+      <c r="E15" s="1217"/>
+      <c r="F15" s="1217"/>
+      <c r="G15" s="1217"/>
+      <c r="H15" s="1217"/>
+      <c r="I15" s="1217"/>
+      <c r="J15" s="1217"/>
+      <c r="K15" s="1217"/>
+      <c r="L15" s="1217"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B16" s="1232"/>
-      <c r="C16" s="1232"/>
-      <c r="D16" s="1232"/>
-      <c r="E16" s="1232"/>
-      <c r="F16" s="1232"/>
-      <c r="G16" s="1232"/>
-      <c r="H16" s="1232"/>
-      <c r="I16" s="1232"/>
-      <c r="J16" s="1232"/>
-      <c r="K16" s="1232"/>
-      <c r="L16" s="1232"/>
+      <c r="B16" s="1218"/>
+      <c r="C16" s="1218"/>
+      <c r="D16" s="1218"/>
+      <c r="E16" s="1218"/>
+      <c r="F16" s="1218"/>
+      <c r="G16" s="1218"/>
+      <c r="H16" s="1218"/>
+      <c r="I16" s="1218"/>
+      <c r="J16" s="1218"/>
+      <c r="K16" s="1218"/>
+      <c r="L16" s="1218"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B17" s="1225" t="s">
+      <c r="B17" s="1211" t="s">
         <v>488</v>
       </c>
-      <c r="C17" s="1226"/>
-      <c r="D17" s="1226"/>
-      <c r="E17" s="1226"/>
-      <c r="F17" s="1226"/>
-      <c r="G17" s="1226"/>
-      <c r="H17" s="1226"/>
-      <c r="I17" s="1226"/>
-      <c r="J17" s="1226"/>
-      <c r="K17" s="1226"/>
-      <c r="L17" s="1227"/>
+      <c r="C17" s="1212"/>
+      <c r="D17" s="1212"/>
+      <c r="E17" s="1212"/>
+      <c r="F17" s="1212"/>
+      <c r="G17" s="1212"/>
+      <c r="H17" s="1212"/>
+      <c r="I17" s="1212"/>
+      <c r="J17" s="1212"/>
+      <c r="K17" s="1212"/>
+      <c r="L17" s="1213"/>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" s="820"/>
@@ -29088,23 +29076,23 @@
       <c r="E25" s="850" t="s">
         <v>42</v>
       </c>
-      <c r="F25" s="1198" t="s">
+      <c r="F25" s="1204" t="s">
         <v>500</v>
       </c>
-      <c r="G25" s="1199"/>
-      <c r="H25" s="1198" t="s">
+      <c r="G25" s="1206"/>
+      <c r="H25" s="1204" t="s">
         <v>501</v>
       </c>
-      <c r="I25" s="1222"/>
-      <c r="J25" s="1199"/>
+      <c r="I25" s="1205"/>
+      <c r="J25" s="1206"/>
       <c r="K25" s="312"/>
       <c r="L25" s="312"/>
     </row>
     <row r="26" spans="2:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="1198" t="s">
+      <c r="B26" s="1204" t="s">
         <v>502</v>
       </c>
-      <c r="C26" s="1199"/>
+      <c r="C26" s="1206"/>
       <c r="D26" s="852" t="s">
         <v>503</v>
       </c>
@@ -29117,10 +29105,10 @@
       <c r="G26" s="853" t="s">
         <v>504</v>
       </c>
-      <c r="H26" s="1198" t="s">
+      <c r="H26" s="1204" t="s">
         <v>505</v>
       </c>
-      <c r="I26" s="1199"/>
+      <c r="I26" s="1206"/>
       <c r="J26" s="853" t="s">
         <v>504</v>
       </c>
@@ -29138,8 +29126,8 @@
       <c r="E27" s="855"/>
       <c r="F27" s="854"/>
       <c r="G27" s="856"/>
-      <c r="H27" s="1223"/>
-      <c r="I27" s="1224"/>
+      <c r="H27" s="1207"/>
+      <c r="I27" s="1208"/>
       <c r="J27" s="856"/>
       <c r="K27" s="312"/>
       <c r="L27" s="312"/>
@@ -29159,8 +29147,8 @@
       <c r="G28" s="859">
         <v>0</v>
       </c>
-      <c r="H28" s="1200"/>
-      <c r="I28" s="1201"/>
+      <c r="H28" s="1209"/>
+      <c r="I28" s="1210"/>
       <c r="J28" s="860">
         <v>0</v>
       </c>
@@ -29182,8 +29170,8 @@
       <c r="G29" s="859">
         <v>156.9</v>
       </c>
-      <c r="H29" s="1200"/>
-      <c r="I29" s="1201"/>
+      <c r="H29" s="1209"/>
+      <c r="I29" s="1210"/>
       <c r="J29" s="860">
         <v>133.4</v>
       </c>
@@ -29205,8 +29193,8 @@
       <c r="G30" s="859">
         <v>96.4</v>
       </c>
-      <c r="H30" s="1200"/>
-      <c r="I30" s="1201"/>
+      <c r="H30" s="1209"/>
+      <c r="I30" s="1210"/>
       <c r="J30" s="860">
         <v>62.8</v>
       </c>
@@ -29230,8 +29218,8 @@
       <c r="G31" s="863">
         <v>72.3</v>
       </c>
-      <c r="H31" s="1194"/>
-      <c r="I31" s="1195"/>
+      <c r="H31" s="1230"/>
+      <c r="I31" s="1231"/>
       <c r="J31" s="864">
         <v>33.4</v>
       </c>
@@ -29241,10 +29229,10 @@
       <c r="Q31" s="802"/>
     </row>
     <row r="32" spans="2:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="1198" t="s">
+      <c r="B32" s="1204" t="s">
         <v>506</v>
       </c>
-      <c r="C32" s="1199"/>
+      <c r="C32" s="1206"/>
       <c r="D32" s="852"/>
       <c r="E32" s="865">
         <f>SUM(E28:E31)</f>
@@ -29255,8 +29243,8 @@
         <f>SUM(G28:G31)</f>
         <v>325.60000000000002</v>
       </c>
-      <c r="H32" s="1196"/>
-      <c r="I32" s="1197"/>
+      <c r="H32" s="1232"/>
+      <c r="I32" s="1233"/>
       <c r="J32" s="865">
         <f>SUM(J28:J31)</f>
         <v>229.6</v>
@@ -29267,10 +29255,10 @@
       <c r="Q32" s="802"/>
     </row>
     <row r="33" spans="2:12" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="1198" t="s">
+      <c r="B33" s="1204" t="s">
         <v>507</v>
       </c>
-      <c r="C33" s="1199"/>
+      <c r="C33" s="1206"/>
       <c r="D33" s="852"/>
       <c r="E33" s="865"/>
       <c r="F33" s="867"/>
@@ -29278,8 +29266,8 @@
         <f>G32/E32*100</f>
         <v>1.4259437680651661</v>
       </c>
-      <c r="H33" s="1196"/>
-      <c r="I33" s="1197"/>
+      <c r="H33" s="1232"/>
+      <c r="I33" s="1233"/>
       <c r="J33" s="865">
         <f>J32/E32*100</f>
         <v>1.0055180870631513</v>
@@ -29299,26 +29287,26 @@
       <c r="J34" s="142"/>
     </row>
     <row r="35" spans="2:12" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H35" s="1202" t="s">
+      <c r="H35" s="1219" t="s">
         <v>508</v>
       </c>
-      <c r="I35" s="1203"/>
-      <c r="J35" s="1204"/>
+      <c r="I35" s="1220"/>
+      <c r="J35" s="1221"/>
     </row>
     <row r="36" spans="2:12" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H36" s="1207" t="s">
+      <c r="H36" s="1224" t="s">
         <v>509</v>
       </c>
-      <c r="I36" s="1208"/>
-      <c r="J36" s="1211">
+      <c r="I36" s="1225"/>
+      <c r="J36" s="1228">
         <f>G33+J33</f>
         <v>2.4314618551283171</v>
       </c>
     </row>
     <row r="37" spans="2:12" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H37" s="1209"/>
-      <c r="I37" s="1210"/>
-      <c r="J37" s="1212"/>
+      <c r="H37" s="1226"/>
+      <c r="I37" s="1227"/>
+      <c r="J37" s="1229"/>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.25">
       <c r="G39" s="140"/>
@@ -29333,16 +29321,16 @@
       <c r="H40" s="140"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B41" s="1087"/>
-      <c r="C41" s="1087"/>
-      <c r="D41" s="1087"/>
-      <c r="E41" s="1206"/>
+      <c r="B41" s="1088"/>
+      <c r="C41" s="1088"/>
+      <c r="D41" s="1088"/>
+      <c r="E41" s="1223"/>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B42" s="1087"/>
-      <c r="C42" s="1087"/>
-      <c r="D42" s="1087"/>
-      <c r="E42" s="1206"/>
+      <c r="B42" s="1088"/>
+      <c r="C42" s="1088"/>
+      <c r="D42" s="1088"/>
+      <c r="E42" s="1223"/>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.25">
       <c r="F43" s="140"/>
@@ -29371,19 +29359,19 @@
       <c r="D56" s="839"/>
     </row>
     <row r="58" spans="2:12" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="1205" t="s">
+      <c r="B58" s="1222" t="s">
         <v>513</v>
       </c>
-      <c r="C58" s="1205"/>
-      <c r="D58" s="1205"/>
-      <c r="E58" s="1205"/>
-      <c r="F58" s="1205"/>
-      <c r="G58" s="1205"/>
-      <c r="H58" s="1205"/>
-      <c r="I58" s="1205"/>
-      <c r="J58" s="1205"/>
-      <c r="K58" s="1205"/>
-      <c r="L58" s="1205"/>
+      <c r="C58" s="1222"/>
+      <c r="D58" s="1222"/>
+      <c r="E58" s="1222"/>
+      <c r="F58" s="1222"/>
+      <c r="G58" s="1222"/>
+      <c r="H58" s="1222"/>
+      <c r="I58" s="1222"/>
+      <c r="J58" s="1222"/>
+      <c r="K58" s="1222"/>
+      <c r="L58" s="1222"/>
     </row>
   </sheetData>
   <protectedRanges>
@@ -29392,6 +29380,19 @@
     <protectedRange sqref="D18" name="Rango3_3_1_1_1_1_1_1_1_1_2"/>
   </protectedRanges>
   <mergeCells count="24">
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="B58:L58"/>
+    <mergeCell ref="B41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="H36:I37"/>
+    <mergeCell ref="J36:J37"/>
     <mergeCell ref="B1:L5"/>
     <mergeCell ref="H25:J25"/>
     <mergeCell ref="H27:I27"/>
@@ -29403,19 +29404,6 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="B15:L16"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="B58:L58"/>
-    <mergeCell ref="B41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="H36:I37"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="H30:I30"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -29500,28 +29488,28 @@
       <c r="G6" s="905"/>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1238" t="s">
+      <c r="A7" s="1234" t="s">
         <v>476</v>
       </c>
-      <c r="B7" s="1238"/>
-      <c r="C7" s="1238"/>
-      <c r="D7" s="1238"/>
-      <c r="E7" s="1238"/>
-      <c r="F7" s="1238"/>
-      <c r="G7" s="1238"/>
-      <c r="H7" s="1238"/>
+      <c r="B7" s="1234"/>
+      <c r="C7" s="1234"/>
+      <c r="D7" s="1234"/>
+      <c r="E7" s="1234"/>
+      <c r="F7" s="1234"/>
+      <c r="G7" s="1234"/>
+      <c r="H7" s="1234"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1239" t="s">
-        <v>578</v>
-      </c>
-      <c r="B8" s="1239"/>
-      <c r="C8" s="1239"/>
-      <c r="D8" s="1239"/>
-      <c r="E8" s="1239"/>
-      <c r="F8" s="1239"/>
-      <c r="G8" s="1239"/>
-      <c r="H8" s="1239"/>
+      <c r="A8" s="1235" t="s">
+        <v>576</v>
+      </c>
+      <c r="B8" s="1235"/>
+      <c r="C8" s="1235"/>
+      <c r="D8" s="1235"/>
+      <c r="E8" s="1235"/>
+      <c r="F8" s="1235"/>
+      <c r="G8" s="1235"/>
+      <c r="H8" s="1235"/>
       <c r="I8"/>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -29536,27 +29524,27 @@
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="846"/>
-      <c r="C10" s="1261" t="s">
+      <c r="C10" s="980" t="s">
+        <v>579</v>
+      </c>
+      <c r="D10" s="980" t="s">
+        <v>580</v>
+      </c>
+      <c r="E10" s="980" t="s">
         <v>581</v>
       </c>
-      <c r="D10" s="1261" t="s">
+      <c r="F10" s="980" t="s">
         <v>582</v>
-      </c>
-      <c r="E10" s="1261" t="s">
-        <v>583</v>
-      </c>
-      <c r="F10" s="1261" t="s">
-        <v>584</v>
       </c>
       <c r="G10" s="888"/>
       <c r="I10"/>
     </row>
     <row r="11" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="846"/>
-      <c r="C11" s="1261"/>
-      <c r="D11" s="1261"/>
-      <c r="E11" s="1261"/>
-      <c r="F11" s="1261"/>
+      <c r="C11" s="980"/>
+      <c r="D11" s="980"/>
+      <c r="E11" s="980"/>
+      <c r="F11" s="980"/>
       <c r="I11"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -29567,29 +29555,29 @@
       <c r="I12"/>
     </row>
     <row r="13" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1240" t="s">
-        <v>535</v>
-      </c>
-      <c r="B13" s="1241"/>
-      <c r="C13" s="1241"/>
-      <c r="D13" s="1241"/>
-      <c r="E13" s="1241"/>
-      <c r="F13" s="1241"/>
-      <c r="G13" s="1241"/>
-      <c r="H13" s="1242"/>
+      <c r="A13" s="1236" t="s">
+        <v>533</v>
+      </c>
+      <c r="B13" s="1237"/>
+      <c r="C13" s="1237"/>
+      <c r="D13" s="1237"/>
+      <c r="E13" s="1237"/>
+      <c r="F13" s="1237"/>
+      <c r="G13" s="1237"/>
+      <c r="H13" s="1238"/>
       <c r="I13"/>
     </row>
     <row r="14" spans="1:9" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1243" t="s">
-        <v>536</v>
-      </c>
-      <c r="B14" s="1244"/>
-      <c r="C14" s="1244"/>
-      <c r="D14" s="1244"/>
-      <c r="E14" s="1244"/>
-      <c r="F14" s="1244"/>
-      <c r="G14" s="1244"/>
-      <c r="H14" s="1245"/>
+      <c r="A14" s="1239" t="s">
+        <v>534</v>
+      </c>
+      <c r="B14" s="1240"/>
+      <c r="C14" s="1240"/>
+      <c r="D14" s="1240"/>
+      <c r="E14" s="1240"/>
+      <c r="F14" s="1240"/>
+      <c r="G14" s="1240"/>
+      <c r="H14" s="1241"/>
     </row>
     <row r="15" spans="1:9" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="889"/>
@@ -29602,15 +29590,15 @@
       <c r="H15" s="934"/>
     </row>
     <row r="16" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="1236" t="s">
-        <v>537</v>
-      </c>
-      <c r="B16" s="1237"/>
+      <c r="A16" s="1243" t="s">
+        <v>535</v>
+      </c>
+      <c r="B16" s="1244"/>
       <c r="C16" s="977" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E16" s="970" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="F16" s="892"/>
       <c r="G16" s="909"/>
@@ -29619,7 +29607,7 @@
     <row r="17" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="936"/>
       <c r="E17" s="970" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="F17" s="250"/>
       <c r="G17" s="909"/>
@@ -29630,7 +29618,7 @@
       <c r="B18" s="936"/>
       <c r="C18" s="936"/>
       <c r="E18" s="970" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F18" s="936"/>
       <c r="G18" s="909"/>
@@ -29658,7 +29646,7 @@
     </row>
     <row r="21" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="972" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B21" s="380"/>
       <c r="C21" s="380"/>
@@ -29671,7 +29659,7 @@
     <row r="22" spans="1:14" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A22" s="973"/>
       <c r="B22" s="964" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C22" s="965"/>
       <c r="D22" s="965"/>
@@ -29683,16 +29671,16 @@
     <row r="23" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="973"/>
       <c r="B23" s="947" t="s">
+        <v>540</v>
+      </c>
+      <c r="C23" s="940" t="s">
+        <v>541</v>
+      </c>
+      <c r="D23" s="941" t="s">
         <v>542</v>
       </c>
-      <c r="C23" s="940" t="s">
-        <v>543</v>
-      </c>
-      <c r="D23" s="941" t="s">
-        <v>544</v>
-      </c>
       <c r="E23" s="941" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F23" s="967"/>
       <c r="G23" s="968"/>
@@ -29701,56 +29689,52 @@
     <row r="24" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="973"/>
       <c r="B24" s="956" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C24" s="941" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D24" s="942"/>
       <c r="E24" s="941" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="F24" s="943"/>
       <c r="G24" s="950"/>
       <c r="H24" s="935"/>
-      <c r="K24" s="1233" t="s">
-        <v>514</v>
-      </c>
-      <c r="L24" s="1233"/>
-      <c r="M24" s="1233"/>
+      <c r="K24"/>
+      <c r="L24"/>
+      <c r="M24"/>
     </row>
     <row r="25" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="973"/>
       <c r="B25" s="956" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C25" s="941" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D25" s="942"/>
       <c r="E25" s="941" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F25" s="943"/>
       <c r="G25" s="950"/>
       <c r="H25" s="935"/>
-      <c r="K25" s="1234" t="s">
-        <v>515</v>
-      </c>
-      <c r="L25" s="1234"/>
-      <c r="M25" s="1234"/>
+      <c r="K25"/>
+      <c r="L25"/>
+      <c r="M25"/>
     </row>
     <row r="26" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="973"/>
       <c r="B26" s="956" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C26" s="941" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D26" s="942"/>
       <c r="E26" s="941" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="F26" s="943"/>
       <c r="G26" s="950"/>
@@ -29759,14 +29743,14 @@
     <row r="27" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="973"/>
       <c r="B27" s="956" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C27" s="941" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D27" s="942"/>
       <c r="E27" s="941" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="F27" s="943"/>
       <c r="G27" s="950"/>
@@ -29775,7 +29759,7 @@
     <row r="28" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="973"/>
       <c r="B28" s="963" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C28" s="959"/>
       <c r="D28" s="959"/>
@@ -29792,7 +29776,7 @@
     <row r="29" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="973"/>
       <c r="B29" s="969" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C29" s="970"/>
       <c r="D29" s="970"/>
@@ -29807,22 +29791,22 @@
     <row r="30" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="973"/>
       <c r="B30" s="948" t="s">
+        <v>551</v>
+      </c>
+      <c r="C30" s="944" t="s">
+        <v>552</v>
+      </c>
+      <c r="D30" s="944" t="s">
         <v>553</v>
       </c>
-      <c r="C30" s="944" t="s">
+      <c r="E30" s="944" t="s">
         <v>554</v>
       </c>
-      <c r="D30" s="944" t="s">
+      <c r="F30" s="944" t="s">
         <v>555</v>
       </c>
-      <c r="E30" s="944" t="s">
+      <c r="G30" s="949" t="s">
         <v>556</v>
-      </c>
-      <c r="F30" s="944" t="s">
-        <v>557</v>
-      </c>
-      <c r="G30" s="949" t="s">
-        <v>558</v>
       </c>
       <c r="H30" s="937"/>
       <c r="L30" s="930"/>
@@ -29832,7 +29816,7 @@
     <row r="31" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="973"/>
       <c r="B31" s="963" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C31" s="941">
         <v>1</v>
@@ -29879,7 +29863,7 @@
     <row r="33" spans="1:14" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A33" s="973"/>
       <c r="B33" s="964" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C33" s="965"/>
       <c r="D33" s="965"/>
@@ -29894,16 +29878,16 @@
     <row r="34" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="973"/>
       <c r="B34" s="947" t="s">
+        <v>540</v>
+      </c>
+      <c r="C34" s="940" t="s">
+        <v>541</v>
+      </c>
+      <c r="D34" s="941" t="s">
         <v>542</v>
       </c>
-      <c r="C34" s="940" t="s">
+      <c r="E34" s="941" t="s">
         <v>543</v>
-      </c>
-      <c r="D34" s="941" t="s">
-        <v>544</v>
-      </c>
-      <c r="E34" s="941" t="s">
-        <v>545</v>
       </c>
       <c r="F34" s="970"/>
       <c r="G34" s="968"/>
@@ -29915,14 +29899,14 @@
     <row r="35" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="973"/>
       <c r="B35" s="956" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C35" s="941" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D35" s="942"/>
       <c r="E35" s="941" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F35" s="970"/>
       <c r="G35" s="968"/>
@@ -29934,14 +29918,14 @@
     <row r="36" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="973"/>
       <c r="B36" s="956" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C36" s="941" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D36" s="942"/>
       <c r="E36" s="941" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F36" s="970"/>
       <c r="G36" s="968"/>
@@ -29953,14 +29937,14 @@
     <row r="37" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="973"/>
       <c r="B37" s="956" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C37" s="941" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D37" s="942"/>
       <c r="E37" s="941" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F37" s="970"/>
       <c r="G37" s="968"/>
@@ -29972,7 +29956,7 @@
     <row r="38" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="973"/>
       <c r="B38" s="963" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C38" s="959"/>
       <c r="D38" s="941"/>
@@ -29987,7 +29971,7 @@
     <row r="39" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="973"/>
       <c r="B39" s="969" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C39" s="955"/>
       <c r="D39" s="955"/>
@@ -30002,22 +29986,22 @@
     <row r="40" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="973"/>
       <c r="B40" s="948" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C40" s="944" t="s">
+        <v>552</v>
+      </c>
+      <c r="D40" s="944" t="s">
+        <v>553</v>
+      </c>
+      <c r="E40" s="944" t="s">
         <v>554</v>
       </c>
-      <c r="D40" s="944" t="s">
+      <c r="F40" s="944" t="s">
         <v>555</v>
       </c>
-      <c r="E40" s="944" t="s">
-        <v>556</v>
-      </c>
-      <c r="F40" s="944" t="s">
-        <v>557</v>
-      </c>
       <c r="G40" s="949" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H40" s="907"/>
       <c r="L40" s="930"/>
@@ -30027,7 +30011,7 @@
     <row r="41" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="973"/>
       <c r="B41" s="963" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C41" s="941">
         <v>1</v>
@@ -30071,7 +30055,7 @@
     <row r="43" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="973"/>
       <c r="B43" s="963" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C43" s="941">
         <v>1</v>
@@ -30115,7 +30099,7 @@
     <row r="45" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="973"/>
       <c r="B45" s="963" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C45" s="941">
         <v>1</v>
@@ -30162,7 +30146,7 @@
     <row r="47" spans="1:14" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A47" s="973"/>
       <c r="B47" s="964" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C47" s="965"/>
       <c r="D47" s="965"/>
@@ -30174,16 +30158,16 @@
     <row r="48" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="973"/>
       <c r="B48" s="947" t="s">
+        <v>540</v>
+      </c>
+      <c r="C48" s="940" t="s">
+        <v>541</v>
+      </c>
+      <c r="D48" s="941" t="s">
         <v>542</v>
       </c>
-      <c r="C48" s="940" t="s">
+      <c r="E48" s="941" t="s">
         <v>543</v>
-      </c>
-      <c r="D48" s="941" t="s">
-        <v>544</v>
-      </c>
-      <c r="E48" s="941" t="s">
-        <v>545</v>
       </c>
       <c r="F48" s="967"/>
       <c r="G48" s="968"/>
@@ -30192,14 +30176,14 @@
     <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="973"/>
       <c r="B49" s="956" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C49" s="941" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D49" s="942"/>
       <c r="E49" s="941" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F49" s="943"/>
       <c r="G49" s="950"/>
@@ -30208,7 +30192,7 @@
     <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="973"/>
       <c r="B50" s="963" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C50" s="959"/>
       <c r="D50" s="971"/>
@@ -30222,7 +30206,7 @@
     <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="973"/>
       <c r="B51" s="969" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C51" s="955"/>
       <c r="D51" s="955"/>
@@ -30234,29 +30218,29 @@
     <row r="52" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="973"/>
       <c r="B52" s="948" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C52" s="944" t="s">
+        <v>552</v>
+      </c>
+      <c r="D52" s="944" t="s">
+        <v>553</v>
+      </c>
+      <c r="E52" s="944" t="s">
         <v>554</v>
       </c>
-      <c r="D52" s="944" t="s">
+      <c r="F52" s="944" t="s">
         <v>555</v>
       </c>
-      <c r="E52" s="944" t="s">
-        <v>556</v>
-      </c>
-      <c r="F52" s="944" t="s">
-        <v>557</v>
-      </c>
       <c r="G52" s="949" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H52" s="898"/>
     </row>
     <row r="53" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="973"/>
       <c r="B53" s="963" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C53" s="941">
         <v>1</v>
@@ -30316,16 +30300,16 @@
     </row>
     <row r="57" spans="1:8" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="923" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B57" s="924"/>
       <c r="C57" s="925"/>
       <c r="D57" s="924"/>
       <c r="E57" s="926"/>
-      <c r="F57" s="1235" t="s">
-        <v>530</v>
-      </c>
-      <c r="G57" s="1235"/>
+      <c r="F57" s="1242" t="s">
+        <v>528</v>
+      </c>
+      <c r="G57" s="1242"/>
       <c r="H57" s="974"/>
     </row>
     <row r="58" spans="1:8" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -30335,7 +30319,7 @@
       <c r="D58" s="929"/>
       <c r="E58" s="927"/>
       <c r="F58" s="978" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="G58" s="975"/>
     </row>
@@ -30346,7 +30330,7 @@
       <c r="D59" s="901"/>
       <c r="E59" s="891"/>
       <c r="F59" s="979" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="G59" s="976"/>
       <c r="H59" s="910"/>
@@ -30358,7 +30342,7 @@
       <c r="D60" s="901"/>
       <c r="E60" s="891"/>
       <c r="F60" s="979" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="G60" s="976"/>
       <c r="H60" s="910"/>
@@ -30396,39 +30380,37 @@
     </row>
     <row r="65" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="841" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B65" s="908"/>
     </row>
     <row r="66" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D66" s="1086"/>
-      <c r="E66" s="1086"/>
+      <c r="D66" s="1087"/>
+      <c r="E66" s="1087"/>
     </row>
     <row r="67" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="68" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="1205" t="s">
-        <v>577</v>
-      </c>
-      <c r="B68" s="1205"/>
-      <c r="C68" s="1205"/>
-      <c r="D68" s="1205"/>
-      <c r="E68" s="1205"/>
-      <c r="F68" s="1205"/>
-      <c r="G68" s="1205"/>
-      <c r="H68" s="1205"/>
+      <c r="A68" s="1222" t="s">
+        <v>575</v>
+      </c>
+      <c r="B68" s="1222"/>
+      <c r="C68" s="1222"/>
+      <c r="D68" s="1222"/>
+      <c r="E68" s="1222"/>
+      <c r="F68" s="1222"/>
+      <c r="G68" s="1222"/>
+      <c r="H68" s="1222"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="8">
+    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="D66:E66"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A68:H68"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="E24:E27">
@@ -30478,7 +30460,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="10.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="156" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B1" s="214"/>
       <c r="C1" s="214"/>
@@ -30490,7 +30472,7 @@
     </row>
     <row r="2" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="157" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B2" s="216"/>
       <c r="C2" s="216"/>
@@ -30502,13 +30484,13 @@
     </row>
     <row r="3" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="158" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H3" s="218"/>
     </row>
     <row r="4" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="158" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B4" s="135"/>
       <c r="C4" s="135"/>
@@ -30520,7 +30502,7 @@
     </row>
     <row r="5" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="158" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B5" s="135"/>
       <c r="C5" s="135"/>
@@ -30532,7 +30514,7 @@
     </row>
     <row r="6" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="158" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B6" s="135"/>
       <c r="C6" s="135"/>
@@ -30583,40 +30565,40 @@
       <c r="H10" s="135"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="1190" t="s">
+      <c r="A11" s="1191" t="s">
+        <v>520</v>
+      </c>
+      <c r="B11" s="1191"/>
+      <c r="C11" s="1191"/>
+      <c r="D11" s="1191"/>
+      <c r="E11" s="1191"/>
+      <c r="F11" s="1191"/>
+      <c r="G11" s="1191"/>
+      <c r="H11" s="1191"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="1246" t="s">
+        <v>521</v>
+      </c>
+      <c r="B12" s="1246"/>
+      <c r="C12" s="1246"/>
+      <c r="D12" s="1246"/>
+      <c r="E12" s="1246"/>
+      <c r="F12" s="1246"/>
+      <c r="G12" s="1246"/>
+      <c r="H12" s="1246"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="1246" t="s">
         <v>522</v>
       </c>
-      <c r="B11" s="1190"/>
-      <c r="C11" s="1190"/>
-      <c r="D11" s="1190"/>
-      <c r="E11" s="1190"/>
-      <c r="F11" s="1190"/>
-      <c r="G11" s="1190"/>
-      <c r="H11" s="1190"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="1247" t="s">
-        <v>523</v>
-      </c>
-      <c r="B12" s="1247"/>
-      <c r="C12" s="1247"/>
-      <c r="D12" s="1247"/>
-      <c r="E12" s="1247"/>
-      <c r="F12" s="1247"/>
-      <c r="G12" s="1247"/>
-      <c r="H12" s="1247"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="1247" t="s">
-        <v>524</v>
-      </c>
-      <c r="B13" s="1247"/>
-      <c r="C13" s="1247"/>
-      <c r="D13" s="1247"/>
-      <c r="E13" s="1247"/>
-      <c r="F13" s="1247"/>
-      <c r="G13" s="1247"/>
-      <c r="H13" s="1247"/>
+      <c r="B13" s="1246"/>
+      <c r="C13" s="1246"/>
+      <c r="D13" s="1246"/>
+      <c r="E13" s="1246"/>
+      <c r="F13" s="1246"/>
+      <c r="G13" s="1246"/>
+      <c r="H13" s="1246"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="144" t="e">
@@ -30704,77 +30686,77 @@
       <c r="D23" s="149"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="1248" t="s">
+      <c r="A26" s="1247" t="s">
         <v>466</v>
       </c>
-      <c r="B26" s="1248"/>
-      <c r="C26" s="1248"/>
-      <c r="D26" s="1248"/>
-      <c r="E26" s="1248"/>
-      <c r="F26" s="1248"/>
-      <c r="G26" s="1248"/>
-      <c r="H26" s="1248"/>
+      <c r="B26" s="1247"/>
+      <c r="C26" s="1247"/>
+      <c r="D26" s="1247"/>
+      <c r="E26" s="1247"/>
+      <c r="F26" s="1247"/>
+      <c r="G26" s="1247"/>
+      <c r="H26" s="1247"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="1249" t="s">
+      <c r="A29" s="1248" t="s">
         <v>229</v>
       </c>
-      <c r="B29" s="1251" t="s">
-        <v>525</v>
-      </c>
-      <c r="C29" s="1252"/>
-      <c r="D29" s="1252"/>
-      <c r="E29" s="1252"/>
-      <c r="F29" s="1253"/>
-      <c r="G29" s="1257">
+      <c r="B29" s="1250" t="s">
+        <v>523</v>
+      </c>
+      <c r="C29" s="1251"/>
+      <c r="D29" s="1251"/>
+      <c r="E29" s="1251"/>
+      <c r="F29" s="1252"/>
+      <c r="G29" s="1256">
         <v>1582.4</v>
       </c>
-      <c r="H29" s="1259" t="s">
-        <v>526</v>
+      <c r="H29" s="1258" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="1250"/>
-      <c r="B30" s="1254"/>
-      <c r="C30" s="1255"/>
-      <c r="D30" s="1255"/>
-      <c r="E30" s="1255"/>
-      <c r="F30" s="1256"/>
-      <c r="G30" s="1258"/>
-      <c r="H30" s="1260"/>
+      <c r="A30" s="1249"/>
+      <c r="B30" s="1253"/>
+      <c r="C30" s="1254"/>
+      <c r="D30" s="1254"/>
+      <c r="E30" s="1254"/>
+      <c r="F30" s="1255"/>
+      <c r="G30" s="1257"/>
+      <c r="H30" s="1259"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="150" t="s">
         <v>230</v>
       </c>
-      <c r="B31" s="1251" t="s">
-        <v>527</v>
-      </c>
-      <c r="C31" s="1252"/>
-      <c r="D31" s="1252"/>
-      <c r="E31" s="1252"/>
-      <c r="F31" s="1253"/>
-      <c r="G31" s="1257"/>
-      <c r="H31" s="1259" t="s">
-        <v>526</v>
+      <c r="B31" s="1250" t="s">
+        <v>525</v>
+      </c>
+      <c r="C31" s="1251"/>
+      <c r="D31" s="1251"/>
+      <c r="E31" s="1251"/>
+      <c r="F31" s="1252"/>
+      <c r="G31" s="1256"/>
+      <c r="H31" s="1258" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="138"/>
-      <c r="B32" s="1254"/>
-      <c r="C32" s="1255"/>
-      <c r="D32" s="1255"/>
-      <c r="E32" s="1255"/>
-      <c r="F32" s="1256"/>
-      <c r="G32" s="1258"/>
-      <c r="H32" s="1260"/>
+      <c r="B32" s="1253"/>
+      <c r="C32" s="1254"/>
+      <c r="D32" s="1254"/>
+      <c r="E32" s="1254"/>
+      <c r="F32" s="1255"/>
+      <c r="G32" s="1257"/>
+      <c r="H32" s="1259"/>
     </row>
     <row r="33" spans="4:9" x14ac:dyDescent="0.25">
       <c r="G33" s="147"/>
     </row>
     <row r="37" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D37" s="151" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F37" s="152">
         <f>+((G29-G31)/G29*100)/100</f>
@@ -30782,11 +30764,11 @@
       </c>
     </row>
     <row r="45" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D45" s="1246"/>
-      <c r="E45" s="1246"/>
-      <c r="F45" s="1246"/>
-      <c r="G45" s="1246"/>
-      <c r="H45" s="1246"/>
+      <c r="D45" s="1245"/>
+      <c r="E45" s="1245"/>
+      <c r="F45" s="1245"/>
+      <c r="G45" s="1245"/>
+      <c r="H45" s="1245"/>
       <c r="I45" s="135"/>
     </row>
   </sheetData>
@@ -30834,11 +30816,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="11.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1004"/>
-      <c r="B1" s="1004"/>
-      <c r="C1" s="1004"/>
-      <c r="D1" s="1004"/>
-      <c r="E1" s="1004"/>
+      <c r="A1" s="983"/>
+      <c r="B1" s="983"/>
+      <c r="C1" s="983"/>
+      <c r="D1" s="983"/>
+      <c r="E1" s="983"/>
       <c r="F1" s="160"/>
       <c r="G1" s="160"/>
       <c r="H1" s="160"/>
@@ -30851,11 +30833,11 @@
       <c r="O1" s="160"/>
     </row>
     <row r="2" spans="1:24" ht="11.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1004"/>
-      <c r="B2" s="1004"/>
-      <c r="C2" s="1004"/>
-      <c r="D2" s="1004"/>
-      <c r="E2" s="1004"/>
+      <c r="A2" s="983"/>
+      <c r="B2" s="983"/>
+      <c r="C2" s="983"/>
+      <c r="D2" s="983"/>
+      <c r="E2" s="983"/>
       <c r="F2" s="160"/>
       <c r="G2" s="160"/>
       <c r="H2" s="160"/>
@@ -30868,11 +30850,11 @@
       <c r="O2" s="160"/>
     </row>
     <row r="3" spans="1:24" ht="11.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1004"/>
-      <c r="B3" s="1004"/>
-      <c r="C3" s="1004"/>
-      <c r="D3" s="1004"/>
-      <c r="E3" s="1004"/>
+      <c r="A3" s="983"/>
+      <c r="B3" s="983"/>
+      <c r="C3" s="983"/>
+      <c r="D3" s="983"/>
+      <c r="E3" s="983"/>
       <c r="F3" s="169"/>
       <c r="G3" s="169"/>
       <c r="H3" s="169"/>
@@ -30885,11 +30867,11 @@
       <c r="O3" s="169"/>
     </row>
     <row r="4" spans="1:24" ht="11.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1004"/>
-      <c r="B4" s="1004"/>
-      <c r="C4" s="1004"/>
-      <c r="D4" s="1004"/>
-      <c r="E4" s="1004"/>
+      <c r="A4" s="983"/>
+      <c r="B4" s="983"/>
+      <c r="C4" s="983"/>
+      <c r="D4" s="983"/>
+      <c r="E4" s="983"/>
       <c r="F4" s="169"/>
       <c r="G4" s="169"/>
       <c r="H4" s="169"/>
@@ -30904,23 +30886,23 @@
       <c r="O4" s="169"/>
     </row>
     <row r="5" spans="1:24" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1003" t="s">
+      <c r="A5" s="982" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="1003"/>
-      <c r="C5" s="1003"/>
-      <c r="D5" s="1003"/>
-      <c r="E5" s="1003"/>
-      <c r="F5" s="1003"/>
-      <c r="G5" s="1003"/>
-      <c r="H5" s="1003"/>
-      <c r="I5" s="1003"/>
-      <c r="J5" s="1003"/>
-      <c r="K5" s="1003"/>
-      <c r="L5" s="1003"/>
-      <c r="M5" s="1003"/>
-      <c r="N5" s="1003"/>
-      <c r="O5" s="1003"/>
+      <c r="B5" s="982"/>
+      <c r="C5" s="982"/>
+      <c r="D5" s="982"/>
+      <c r="E5" s="982"/>
+      <c r="F5" s="982"/>
+      <c r="G5" s="982"/>
+      <c r="H5" s="982"/>
+      <c r="I5" s="982"/>
+      <c r="J5" s="982"/>
+      <c r="K5" s="982"/>
+      <c r="L5" s="982"/>
+      <c r="M5" s="982"/>
+      <c r="N5" s="982"/>
+      <c r="O5" s="982"/>
     </row>
     <row r="6" spans="1:24" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="211"/>
@@ -31053,10 +31035,10 @@
         <v>17</v>
       </c>
       <c r="B11" s="168"/>
-      <c r="C11" s="989">
+      <c r="C11" s="993">
         <v>38972</v>
       </c>
-      <c r="D11" s="989"/>
+      <c r="D11" s="993"/>
       <c r="E11" s="173"/>
       <c r="F11" s="169"/>
       <c r="G11" s="169"/>
@@ -31186,18 +31168,18 @@
       </c>
       <c r="B16" s="168"/>
       <c r="C16" s="169"/>
-      <c r="D16" s="993">
+      <c r="D16" s="997">
         <v>25681</v>
       </c>
-      <c r="E16" s="993"/>
+      <c r="E16" s="997"/>
       <c r="F16" s="169" t="s">
         <v>29</v>
       </c>
       <c r="G16" s="169"/>
-      <c r="H16" s="993">
+      <c r="H16" s="997">
         <v>384.6</v>
       </c>
-      <c r="I16" s="993"/>
+      <c r="I16" s="997"/>
       <c r="J16" s="169"/>
       <c r="K16" s="162" t="s">
         <v>30</v>
@@ -31236,18 +31218,18 @@
       </c>
       <c r="B17" s="169"/>
       <c r="C17" s="169"/>
-      <c r="D17" s="993">
+      <c r="D17" s="997">
         <v>491.5</v>
       </c>
-      <c r="E17" s="993"/>
+      <c r="E17" s="997"/>
       <c r="F17" s="169" t="s">
         <v>33</v>
       </c>
       <c r="G17" s="169"/>
-      <c r="H17" s="993">
+      <c r="H17" s="997">
         <v>364</v>
       </c>
-      <c r="I17" s="993"/>
+      <c r="I17" s="997"/>
       <c r="J17" s="169"/>
       <c r="K17" s="162" t="s">
         <v>34</v>
@@ -31280,20 +31262,20 @@
       </c>
       <c r="B18" s="169"/>
       <c r="C18" s="169"/>
-      <c r="D18" s="994">
+      <c r="D18" s="998">
         <f>+S30+T28</f>
         <v>24395.311291963379</v>
       </c>
-      <c r="E18" s="994"/>
+      <c r="E18" s="998"/>
       <c r="F18" s="169" t="s">
         <v>36</v>
       </c>
       <c r="G18" s="169"/>
-      <c r="H18" s="994">
+      <c r="H18" s="998">
         <f>(H16-H17)/H17*100</f>
         <v>5.6593406593406659</v>
       </c>
-      <c r="I18" s="994"/>
+      <c r="I18" s="998"/>
       <c r="J18" s="169"/>
       <c r="K18" s="162" t="s">
         <v>37</v>
@@ -31358,10 +31340,10 @@
       </c>
     </row>
     <row r="21" spans="1:24" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="987" t="s">
+      <c r="A21" s="991" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="988"/>
+      <c r="B21" s="992"/>
       <c r="C21" s="179" t="s">
         <v>42</v>
       </c>
@@ -31374,11 +31356,11 @@
       <c r="F21" s="180" t="s">
         <v>44</v>
       </c>
-      <c r="G21" s="981" t="s">
+      <c r="G21" s="985" t="s">
         <v>45</v>
       </c>
-      <c r="H21" s="982"/>
-      <c r="I21" s="983"/>
+      <c r="H21" s="986"/>
+      <c r="I21" s="987"/>
       <c r="J21" s="168"/>
       <c r="K21" s="161" t="s">
         <v>16</v>
@@ -31407,11 +31389,11 @@
       <c r="F22" s="182" t="s">
         <v>51</v>
       </c>
-      <c r="G22" s="984" t="s">
+      <c r="G22" s="988" t="s">
         <v>52</v>
       </c>
-      <c r="H22" s="985"/>
-      <c r="I22" s="986"/>
+      <c r="H22" s="989"/>
+      <c r="I22" s="990"/>
       <c r="J22" s="168"/>
       <c r="K22" s="162" t="s">
         <v>21</v>
@@ -31438,11 +31420,11 @@
       <c r="D23" s="185"/>
       <c r="E23" s="186"/>
       <c r="F23" s="187"/>
-      <c r="G23" s="999" t="s">
+      <c r="G23" s="1003" t="s">
         <v>54</v>
       </c>
-      <c r="H23" s="1000"/>
-      <c r="I23" s="1001"/>
+      <c r="H23" s="1004"/>
+      <c r="I23" s="1005"/>
       <c r="J23" s="190"/>
       <c r="K23" s="162" t="s">
         <v>22</v>
@@ -31476,11 +31458,11 @@
         <f>100-E24</f>
         <v>100</v>
       </c>
-      <c r="G24" s="990" t="s">
+      <c r="G24" s="994" t="s">
         <v>56</v>
       </c>
-      <c r="H24" s="991"/>
-      <c r="I24" s="992"/>
+      <c r="H24" s="995"/>
+      <c r="I24" s="996"/>
       <c r="J24" s="190"/>
       <c r="K24" s="162" t="s">
         <v>25</v>
@@ -32125,10 +32107,10 @@
       <c r="F43" s="438" t="s">
         <v>68</v>
       </c>
-      <c r="G43" s="995" t="s">
+      <c r="G43" s="999" t="s">
         <v>69</v>
       </c>
-      <c r="H43" s="996"/>
+      <c r="H43" s="1000"/>
       <c r="I43" s="432" t="s">
         <v>70</v>
       </c>
@@ -32163,10 +32145,10 @@
       <c r="F44" s="439" t="s">
         <v>73</v>
       </c>
-      <c r="G44" s="997" t="s">
+      <c r="G44" s="1001" t="s">
         <v>69</v>
       </c>
-      <c r="H44" s="998"/>
+      <c r="H44" s="1002"/>
       <c r="I44" s="437" t="s">
         <v>74</v>
       </c>
@@ -32274,10 +32256,10 @@
       <c r="M49" s="169"/>
       <c r="N49" s="169"/>
       <c r="O49" s="169"/>
-      <c r="R49" s="1002" t="s">
+      <c r="R49" s="981" t="s">
         <v>77</v>
       </c>
-      <c r="S49" s="1002"/>
+      <c r="S49" s="981"/>
     </row>
     <row r="50" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="169"/>
@@ -32386,10 +32368,10 @@
       <c r="M54" s="169"/>
       <c r="N54" s="169"/>
       <c r="O54" s="169"/>
-      <c r="R54" s="1002" t="s">
+      <c r="R54" s="981" t="s">
         <v>79</v>
       </c>
-      <c r="S54" s="1002"/>
+      <c r="S54" s="981"/>
       <c r="T54" s="200">
         <f>IF(R52=0,"---",R62/R52)</f>
         <v>38</v>
@@ -32508,10 +32490,10 @@
       <c r="M59" s="169"/>
       <c r="N59" s="169"/>
       <c r="O59" s="169"/>
-      <c r="R59" s="1002" t="s">
+      <c r="R59" s="981" t="s">
         <v>81</v>
       </c>
-      <c r="S59" s="1002"/>
+      <c r="S59" s="981"/>
     </row>
     <row r="60" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="168"/>
@@ -32810,8 +32792,8 @@
       <c r="K78" s="117"/>
       <c r="L78" s="117"/>
       <c r="M78" s="117"/>
-      <c r="N78" s="980"/>
-      <c r="O78" s="980"/>
+      <c r="N78" s="984"/>
+      <c r="O78" s="984"/>
     </row>
     <row r="79" spans="1:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="169"/>
@@ -32832,11 +32814,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="R54:S54"/>
-    <mergeCell ref="R59:S59"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A1:E4"/>
     <mergeCell ref="N78:O78"/>
     <mergeCell ref="G21:I21"/>
     <mergeCell ref="G22:I22"/>
@@ -32852,6 +32829,11 @@
     <mergeCell ref="G44:H44"/>
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="G23:I23"/>
+    <mergeCell ref="R54:S54"/>
+    <mergeCell ref="R59:S59"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="A5:O5"/>
+    <mergeCell ref="A1:E4"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -32877,8 +32859,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1004"/>
-      <c r="B1" s="1004"/>
+      <c r="A1" s="983"/>
+      <c r="B1" s="983"/>
       <c r="C1" s="269"/>
       <c r="D1" s="159"/>
       <c r="E1" s="159"/>
@@ -32886,8 +32868,8 @@
       <c r="G1" s="159"/>
     </row>
     <row r="2" spans="1:7" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1004"/>
-      <c r="B2" s="1004"/>
+      <c r="A2" s="983"/>
+      <c r="B2" s="983"/>
       <c r="C2" s="269"/>
       <c r="D2" s="269"/>
       <c r="E2" s="269"/>
@@ -32895,15 +32877,15 @@
       <c r="G2" s="159"/>
     </row>
     <row r="3" spans="1:7" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1004"/>
-      <c r="B3" s="1004"/>
+      <c r="A3" s="983"/>
+      <c r="B3" s="983"/>
       <c r="C3" s="272"/>
       <c r="D3" s="272"/>
       <c r="E3" s="272"/>
     </row>
     <row r="4" spans="1:7" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1004"/>
-      <c r="B4" s="1004"/>
+      <c r="A4" s="983"/>
+      <c r="B4" s="983"/>
       <c r="D4" s="168"/>
     </row>
     <row r="5" spans="1:7" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -32915,15 +32897,15 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1005" t="s">
+      <c r="A6" s="1006" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="1005"/>
-      <c r="C6" s="1005"/>
-      <c r="D6" s="1005"/>
-      <c r="E6" s="1005"/>
-      <c r="F6" s="1005"/>
-      <c r="G6" s="1005"/>
+      <c r="B6" s="1006"/>
+      <c r="C6" s="1006"/>
+      <c r="D6" s="1006"/>
+      <c r="E6" s="1006"/>
+      <c r="F6" s="1006"/>
+      <c r="G6" s="1006"/>
     </row>
     <row r="7" spans="1:7" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="211"/>
@@ -33048,10 +33030,10 @@
       <c r="B19" s="168"/>
     </row>
     <row r="20" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1007" t="s">
+      <c r="A20" s="1008" t="s">
         <v>93</v>
       </c>
-      <c r="B20" s="1008"/>
+      <c r="B20" s="1009"/>
       <c r="C20" s="294">
         <v>1</v>
       </c>
@@ -33347,10 +33329,10 @@
       <c r="G35" s="305"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="1009" t="s">
+      <c r="A36" s="1010" t="s">
         <v>101</v>
       </c>
-      <c r="B36" s="1010"/>
+      <c r="B36" s="1011"/>
       <c r="C36" s="185">
         <f>+C33/C35*100</f>
         <v>3.1889763779527645</v>
@@ -33470,10 +33452,10 @@
     <row r="62" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="117"/>
       <c r="B62" s="117"/>
-      <c r="D62" s="1006"/>
-      <c r="E62" s="1006"/>
-      <c r="F62" s="980"/>
-      <c r="G62" s="980"/>
+      <c r="D62" s="1007"/>
+      <c r="E62" s="1007"/>
+      <c r="F62" s="984"/>
+      <c r="G62" s="984"/>
     </row>
     <row r="63" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="117"/>
@@ -33495,10 +33477,10 @@
       <c r="A65" s="176" t="s">
         <v>114</v>
       </c>
-      <c r="B65" s="1011" t="s">
+      <c r="B65" s="1012" t="s">
         <v>115</v>
       </c>
-      <c r="C65" s="1011"/>
+      <c r="C65" s="1012"/>
       <c r="D65" s="176" t="s">
         <v>116</v>
       </c>
@@ -33511,9 +33493,9 @@
       <c r="C66" s="117"/>
       <c r="D66" s="117"/>
       <c r="E66" s="117"/>
-      <c r="F66" s="1006"/>
-      <c r="G66" s="1006"/>
-      <c r="H66" s="1006"/>
+      <c r="F66" s="1007"/>
+      <c r="G66" s="1007"/>
+      <c r="H66" s="1007"/>
       <c r="I66" s="117"/>
       <c r="J66" s="117"/>
       <c r="K66" s="117"/>
@@ -33522,9 +33504,9 @@
       <c r="F67" s="117"/>
       <c r="G67" s="117"/>
       <c r="H67" s="117"/>
-      <c r="I67" s="980"/>
-      <c r="J67" s="980"/>
-      <c r="K67" s="980"/>
+      <c r="I67" s="984"/>
+      <c r="J67" s="984"/>
+      <c r="K67" s="984"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -33652,23 +33634,23 @@
       <c r="O6" s="586"/>
     </row>
     <row r="7" spans="1:21" ht="42" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1025" t="s">
+      <c r="A7" s="1014" t="s">
         <v>118</v>
       </c>
-      <c r="B7" s="1025"/>
-      <c r="C7" s="1025"/>
-      <c r="D7" s="1025"/>
-      <c r="E7" s="1025"/>
-      <c r="F7" s="1025"/>
-      <c r="G7" s="1025"/>
-      <c r="H7" s="1025"/>
-      <c r="I7" s="1025"/>
-      <c r="J7" s="1025"/>
-      <c r="K7" s="1025"/>
-      <c r="L7" s="1025"/>
-      <c r="M7" s="1025"/>
-      <c r="N7" s="1025"/>
-      <c r="O7" s="1025"/>
+      <c r="B7" s="1014"/>
+      <c r="C7" s="1014"/>
+      <c r="D7" s="1014"/>
+      <c r="E7" s="1014"/>
+      <c r="F7" s="1014"/>
+      <c r="G7" s="1014"/>
+      <c r="H7" s="1014"/>
+      <c r="I7" s="1014"/>
+      <c r="J7" s="1014"/>
+      <c r="K7" s="1014"/>
+      <c r="L7" s="1014"/>
+      <c r="M7" s="1014"/>
+      <c r="N7" s="1014"/>
+      <c r="O7" s="1014"/>
     </row>
     <row r="8" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="792" t="s">
@@ -33749,10 +33731,10 @@
         <v>130</v>
       </c>
       <c r="M10" s="167"/>
-      <c r="N10" s="1024">
+      <c r="N10" s="1013">
         <v>41951</v>
       </c>
-      <c r="O10" s="1024"/>
+      <c r="O10" s="1013"/>
       <c r="R10" s="117" t="s">
         <v>131</v>
       </c>
@@ -33929,12 +33911,12 @@
       </c>
     </row>
     <row r="16" spans="1:21" s="178" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1019" t="s">
+      <c r="A16" s="1026" t="s">
         <v>142</v>
       </c>
-      <c r="B16" s="1008"/>
-      <c r="C16" s="1019"/>
-      <c r="D16" s="1019"/>
+      <c r="B16" s="1009"/>
+      <c r="C16" s="1026"/>
+      <c r="D16" s="1026"/>
       <c r="E16" s="747">
         <v>15</v>
       </c>
@@ -33945,11 +33927,11 @@
         <v>32</v>
       </c>
       <c r="H16" s="167"/>
-      <c r="I16" s="1007" t="s">
+      <c r="I16" s="1008" t="s">
         <v>102</v>
       </c>
-      <c r="J16" s="1030"/>
-      <c r="K16" s="1008"/>
+      <c r="J16" s="1020"/>
+      <c r="K16" s="1009"/>
       <c r="L16" s="271"/>
       <c r="M16" s="271"/>
       <c r="N16" s="423"/>
@@ -33967,12 +33949,12 @@
       <c r="U16" s="169"/>
     </row>
     <row r="17" spans="1:28" s="178" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1020" t="s">
+      <c r="A17" s="1027" t="s">
         <v>94</v>
       </c>
-      <c r="B17" s="1010"/>
-      <c r="C17" s="1020"/>
-      <c r="D17" s="1020"/>
+      <c r="B17" s="1011"/>
+      <c r="C17" s="1027"/>
+      <c r="D17" s="1027"/>
       <c r="E17" s="235">
         <v>5</v>
       </c>
@@ -33983,11 +33965,11 @@
         <v>5</v>
       </c>
       <c r="H17" s="167"/>
-      <c r="I17" s="1009" t="s">
+      <c r="I17" s="1010" t="s">
         <v>143</v>
       </c>
-      <c r="J17" s="1027"/>
-      <c r="K17" s="1010"/>
+      <c r="J17" s="1016"/>
+      <c r="K17" s="1011"/>
       <c r="L17" s="751">
         <v>516.29999999999995</v>
       </c>
@@ -34011,12 +33993,12 @@
       <c r="U17" s="169"/>
     </row>
     <row r="18" spans="1:28" s="178" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1020" t="s">
+      <c r="A18" s="1027" t="s">
         <v>95</v>
       </c>
-      <c r="B18" s="1010"/>
-      <c r="C18" s="1020"/>
-      <c r="D18" s="1020"/>
+      <c r="B18" s="1011"/>
+      <c r="C18" s="1027"/>
+      <c r="D18" s="1027"/>
       <c r="E18" s="448">
         <v>56</v>
       </c>
@@ -34027,11 +34009,11 @@
         <v>12</v>
       </c>
       <c r="H18" s="167"/>
-      <c r="I18" s="1009" t="s">
+      <c r="I18" s="1010" t="s">
         <v>144</v>
       </c>
-      <c r="J18" s="1027"/>
-      <c r="K18" s="1010"/>
+      <c r="J18" s="1016"/>
+      <c r="K18" s="1011"/>
       <c r="L18" s="751">
         <v>485.7</v>
       </c>
@@ -34056,12 +34038,12 @@
       <c r="U18" s="169"/>
     </row>
     <row r="19" spans="1:28" s="178" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1020" t="s">
+      <c r="A19" s="1027" t="s">
         <v>96</v>
       </c>
-      <c r="B19" s="1010"/>
-      <c r="C19" s="1020"/>
-      <c r="D19" s="1020"/>
+      <c r="B19" s="1011"/>
+      <c r="C19" s="1027"/>
+      <c r="D19" s="1027"/>
       <c r="E19" s="749">
         <v>12341</v>
       </c>
@@ -34072,11 +34054,11 @@
         <v>12671</v>
       </c>
       <c r="H19" s="167"/>
-      <c r="I19" s="1009" t="s">
+      <c r="I19" s="1010" t="s">
         <v>105</v>
       </c>
-      <c r="J19" s="1027"/>
-      <c r="K19" s="1010"/>
+      <c r="J19" s="1016"/>
+      <c r="K19" s="1011"/>
       <c r="L19" s="229">
         <f>+L17-L18</f>
         <v>30.599999999999966</v>
@@ -34104,12 +34086,12 @@
       <c r="AA19" s="278"/>
     </row>
     <row r="20" spans="1:28" s="178" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1020" t="s">
+      <c r="A20" s="1027" t="s">
         <v>97</v>
       </c>
-      <c r="B20" s="1010"/>
-      <c r="C20" s="1020"/>
-      <c r="D20" s="1020"/>
+      <c r="B20" s="1011"/>
+      <c r="C20" s="1027"/>
+      <c r="D20" s="1027"/>
       <c r="E20" s="749">
         <v>7078</v>
       </c>
@@ -34120,11 +34102,11 @@
         <v>7816</v>
       </c>
       <c r="H20" s="167"/>
-      <c r="I20" s="1009" t="s">
+      <c r="I20" s="1010" t="s">
         <v>106</v>
       </c>
-      <c r="J20" s="1027"/>
-      <c r="K20" s="1010"/>
+      <c r="J20" s="1016"/>
+      <c r="K20" s="1011"/>
       <c r="L20" s="229"/>
       <c r="M20" s="229"/>
       <c r="N20" s="424"/>
@@ -34141,12 +34123,12 @@
       </c>
     </row>
     <row r="21" spans="1:28" s="178" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1020" t="s">
+      <c r="A21" s="1027" t="s">
         <v>98</v>
       </c>
-      <c r="B21" s="1010"/>
-      <c r="C21" s="1020"/>
-      <c r="D21" s="1020"/>
+      <c r="B21" s="1011"/>
+      <c r="C21" s="1027"/>
+      <c r="D21" s="1027"/>
       <c r="E21" s="235">
         <f>+E19-E20</f>
         <v>5263</v>
@@ -34160,11 +34142,11 @@
         <v>4855</v>
       </c>
       <c r="H21" s="167"/>
-      <c r="I21" s="1009" t="s">
+      <c r="I21" s="1010" t="s">
         <v>107</v>
       </c>
-      <c r="J21" s="1027"/>
-      <c r="K21" s="1010"/>
+      <c r="J21" s="1016"/>
+      <c r="K21" s="1011"/>
       <c r="L21" s="229">
         <f>+L18-L20</f>
         <v>485.7</v>
@@ -34193,12 +34175,12 @@
       </c>
     </row>
     <row r="22" spans="1:28" s="178" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1020" t="s">
+      <c r="A22" s="1027" t="s">
         <v>145</v>
       </c>
-      <c r="B22" s="1010"/>
-      <c r="C22" s="1020"/>
-      <c r="D22" s="1020"/>
+      <c r="B22" s="1011"/>
+      <c r="C22" s="1027"/>
+      <c r="D22" s="1027"/>
       <c r="E22" s="749">
         <v>2161</v>
       </c>
@@ -34209,11 +34191,11 @@
         <v>2175</v>
       </c>
       <c r="H22" s="167"/>
-      <c r="I22" s="1009" t="s">
+      <c r="I22" s="1010" t="s">
         <v>101</v>
       </c>
-      <c r="J22" s="1027"/>
-      <c r="K22" s="1010"/>
+      <c r="J22" s="1016"/>
+      <c r="K22" s="1011"/>
       <c r="L22" s="230">
         <f>+L19/L21*100</f>
         <v>6.3001852995676275</v>
@@ -34239,12 +34221,12 @@
       </c>
     </row>
     <row r="23" spans="1:28" s="178" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1022" t="s">
+      <c r="A23" s="1031" t="s">
         <v>146</v>
       </c>
-      <c r="B23" s="1023"/>
-      <c r="C23" s="1022"/>
-      <c r="D23" s="1022"/>
+      <c r="B23" s="1019"/>
+      <c r="C23" s="1031"/>
+      <c r="D23" s="1031"/>
       <c r="E23" s="238">
         <f>+E21/E22</f>
         <v>2.4354465525219804</v>
@@ -34258,11 +34240,11 @@
         <v>2.2321839080459771</v>
       </c>
       <c r="H23" s="167"/>
-      <c r="I23" s="1028" t="s">
+      <c r="I23" s="1017" t="s">
         <v>108</v>
       </c>
-      <c r="J23" s="1029"/>
-      <c r="K23" s="1023"/>
+      <c r="J23" s="1018"/>
+      <c r="K23" s="1019"/>
       <c r="L23" s="240">
         <f>+E23/(1+L22/100)</f>
         <v>2.2911028288977842</v>
@@ -34319,17 +34301,17 @@
       </c>
     </row>
     <row r="25" spans="1:28" s="178" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1032" t="s">
+      <c r="A25" s="1024" t="s">
         <v>147</v>
       </c>
-      <c r="B25" s="1033"/>
-      <c r="C25" s="1033"/>
-      <c r="D25" s="1033"/>
-      <c r="E25" s="1033"/>
-      <c r="F25" s="1033"/>
-      <c r="G25" s="1033"/>
-      <c r="H25" s="1033"/>
-      <c r="I25" s="1033"/>
+      <c r="B25" s="1025"/>
+      <c r="C25" s="1025"/>
+      <c r="D25" s="1025"/>
+      <c r="E25" s="1025"/>
+      <c r="F25" s="1025"/>
+      <c r="G25" s="1025"/>
+      <c r="H25" s="1025"/>
+      <c r="I25" s="1025"/>
       <c r="J25" s="167"/>
       <c r="K25" s="167"/>
       <c r="L25" s="167"/>
@@ -34347,28 +34329,28 @@
       </c>
     </row>
     <row r="26" spans="1:28" s="178" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1012" t="s">
+      <c r="A26" s="1021" t="s">
         <v>148</v>
       </c>
-      <c r="B26" s="1013"/>
+      <c r="B26" s="1023"/>
       <c r="C26" s="227" t="s">
         <v>149</v>
       </c>
-      <c r="D26" s="1012" t="str">
+      <c r="D26" s="1021" t="str">
         <f>+$A$56&amp;" "&amp;C56</f>
         <v>Molde 15</v>
       </c>
-      <c r="E26" s="1013"/>
-      <c r="F26" s="1012" t="str">
+      <c r="E26" s="1023"/>
+      <c r="F26" s="1021" t="str">
         <f>+$A$56&amp;" "&amp;D56</f>
         <v>Molde 10</v>
       </c>
-      <c r="G26" s="1013"/>
-      <c r="H26" s="1012" t="str">
+      <c r="G26" s="1023"/>
+      <c r="H26" s="1021" t="str">
         <f>+$A$56&amp;" "&amp;E56</f>
         <v>Molde 32</v>
       </c>
-      <c r="I26" s="1013"/>
+      <c r="I26" s="1023"/>
       <c r="J26" s="167"/>
       <c r="K26" s="167"/>
       <c r="L26" s="167"/>
@@ -34377,28 +34359,28 @@
       <c r="O26" s="624"/>
     </row>
     <row r="27" spans="1:28" s="178" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1021" t="s">
+      <c r="A27" s="1028" t="s">
         <v>150</v>
       </c>
-      <c r="B27" s="1021" t="s">
+      <c r="B27" s="1028" t="s">
         <v>151</v>
       </c>
       <c r="C27" s="228" t="s">
         <v>152</v>
       </c>
-      <c r="D27" s="1014" t="s">
+      <c r="D27" s="1030" t="s">
         <v>153</v>
       </c>
       <c r="E27" s="228" t="s">
         <v>149</v>
       </c>
-      <c r="F27" s="1014" t="s">
+      <c r="F27" s="1030" t="s">
         <v>153</v>
       </c>
       <c r="G27" s="228" t="s">
         <v>149</v>
       </c>
-      <c r="H27" s="1014" t="s">
+      <c r="H27" s="1030" t="s">
         <v>153</v>
       </c>
       <c r="I27" s="228" t="s">
@@ -34441,20 +34423,20 @@
       </c>
     </row>
     <row r="28" spans="1:28" s="178" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1015"/>
-      <c r="B28" s="1015"/>
+      <c r="A28" s="1029"/>
+      <c r="B28" s="1029"/>
       <c r="C28" s="164" t="s">
         <v>155</v>
       </c>
-      <c r="D28" s="1015"/>
+      <c r="D28" s="1029"/>
       <c r="E28" s="164" t="s">
         <v>155</v>
       </c>
-      <c r="F28" s="1015"/>
+      <c r="F28" s="1029"/>
       <c r="G28" s="164" t="s">
         <v>155</v>
       </c>
-      <c r="H28" s="1015"/>
+      <c r="H28" s="1029"/>
       <c r="I28" s="164" t="s">
         <v>155</v>
       </c>
@@ -34527,14 +34509,14 @@
         <f>+H32/F32</f>
         <v>0.69346733668341709</v>
       </c>
-      <c r="K29" s="1014" t="s">
+      <c r="K29" s="1030" t="s">
         <v>17</v>
       </c>
-      <c r="L29" s="1012" t="s">
+      <c r="L29" s="1021" t="s">
         <v>156</v>
       </c>
-      <c r="M29" s="1031"/>
-      <c r="N29" s="1013"/>
+      <c r="M29" s="1022"/>
+      <c r="N29" s="1023"/>
       <c r="O29" s="624"/>
       <c r="R29" s="117">
         <f t="shared" ref="R29:R38" si="10">+R28+1</f>
@@ -34596,7 +34578,7 @@
         <v>15.777336471729724</v>
       </c>
       <c r="J30" s="167"/>
-      <c r="K30" s="1015"/>
+      <c r="K30" s="1029"/>
       <c r="L30" s="422">
         <f>+E16</f>
         <v>15</v>
@@ -35509,23 +35491,23 @@
       <c r="I51" s="454"/>
     </row>
     <row r="52" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="1026" t="s">
+      <c r="A52" s="1015" t="s">
         <v>159</v>
       </c>
-      <c r="B52" s="1026"/>
-      <c r="C52" s="1026"/>
-      <c r="D52" s="1026"/>
-      <c r="E52" s="1026"/>
-      <c r="F52" s="1026"/>
-      <c r="G52" s="1026"/>
-      <c r="H52" s="1026"/>
-      <c r="I52" s="1026"/>
-      <c r="J52" s="1026"/>
-      <c r="K52" s="1026"/>
-      <c r="L52" s="1026"/>
-      <c r="M52" s="1026"/>
-      <c r="N52" s="1026"/>
-      <c r="O52" s="1026"/>
+      <c r="B52" s="1015"/>
+      <c r="C52" s="1015"/>
+      <c r="D52" s="1015"/>
+      <c r="E52" s="1015"/>
+      <c r="F52" s="1015"/>
+      <c r="G52" s="1015"/>
+      <c r="H52" s="1015"/>
+      <c r="I52" s="1015"/>
+      <c r="J52" s="1015"/>
+      <c r="K52" s="1015"/>
+      <c r="L52" s="1015"/>
+      <c r="M52" s="1015"/>
+      <c r="N52" s="1015"/>
+      <c r="O52" s="1015"/>
       <c r="P52" s="646"/>
       <c r="Q52" s="646"/>
       <c r="R52" s="117">
@@ -35578,30 +35560,30 @@
       <c r="C57" s="244"/>
     </row>
     <row r="58" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="1017" t="s">
+      <c r="A58" s="1033" t="s">
         <v>163</v>
       </c>
-      <c r="B58" s="1017"/>
-      <c r="C58" s="1017"/>
-      <c r="D58" s="1017"/>
-      <c r="E58" s="1017"/>
-      <c r="F58" s="1017"/>
-      <c r="G58" s="1017"/>
-      <c r="H58" s="1017"/>
-      <c r="I58" s="1017"/>
-      <c r="J58" s="1017"/>
+      <c r="B58" s="1033"/>
+      <c r="C58" s="1033"/>
+      <c r="D58" s="1033"/>
+      <c r="E58" s="1033"/>
+      <c r="F58" s="1033"/>
+      <c r="G58" s="1033"/>
+      <c r="H58" s="1033"/>
+      <c r="I58" s="1033"/>
+      <c r="J58" s="1033"/>
     </row>
     <row r="59" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="1017"/>
-      <c r="B59" s="1017"/>
-      <c r="C59" s="1017"/>
-      <c r="D59" s="1017"/>
-      <c r="E59" s="1017"/>
-      <c r="F59" s="1017"/>
-      <c r="G59" s="1017"/>
-      <c r="H59" s="1017"/>
-      <c r="I59" s="1017"/>
-      <c r="J59" s="1017"/>
+      <c r="A59" s="1033"/>
+      <c r="B59" s="1033"/>
+      <c r="C59" s="1033"/>
+      <c r="D59" s="1033"/>
+      <c r="E59" s="1033"/>
+      <c r="F59" s="1033"/>
+      <c r="G59" s="1033"/>
+      <c r="H59" s="1033"/>
+      <c r="I59" s="1033"/>
+      <c r="J59" s="1033"/>
     </row>
     <row r="60" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C60" s="169" t="s">
@@ -35614,17 +35596,17 @@
       </c>
     </row>
     <row r="62" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J62" s="1018"/>
-      <c r="K62" s="1018"/>
+      <c r="J62" s="1034"/>
+      <c r="K62" s="1034"/>
     </row>
     <row r="63" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D63" s="275" t="s">
         <v>166</v>
       </c>
-      <c r="E63" s="1006">
+      <c r="E63" s="1007">
         <v>-10.797347164</v>
       </c>
-      <c r="F63" s="1006"/>
+      <c r="F63" s="1007"/>
       <c r="I63" s="117"/>
       <c r="J63" s="117"/>
       <c r="K63" s="190"/>
@@ -35633,19 +35615,19 @@
       <c r="D64" s="275" t="s">
         <v>167</v>
       </c>
-      <c r="E64" s="1006">
+      <c r="E64" s="1007">
         <v>4.7501944299999996</v>
       </c>
-      <c r="F64" s="1006"/>
+      <c r="F64" s="1007"/>
     </row>
     <row r="65" spans="4:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D65" s="275" t="s">
         <v>168</v>
       </c>
-      <c r="E65" s="1016">
+      <c r="E65" s="1032">
         <v>-7.3115999999999996E-5</v>
       </c>
-      <c r="F65" s="1016"/>
+      <c r="F65" s="1032"/>
     </row>
     <row r="66" spans="4:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D66" s="169" t="s">
@@ -35675,6 +35657,26 @@
     <protectedRange sqref="D10" name="Rango3_3_1_1_1_1_1_1_1_1"/>
   </protectedRanges>
   <mergeCells count="36">
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="A58:J59"/>
+    <mergeCell ref="J62:K62"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="F26:G26"/>
     <mergeCell ref="N10:O10"/>
     <mergeCell ref="A7:O7"/>
     <mergeCell ref="A52:O52"/>
@@ -35691,26 +35693,6 @@
     <mergeCell ref="L29:N29"/>
     <mergeCell ref="A25:I25"/>
     <mergeCell ref="D26:E26"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="A58:J59"/>
-    <mergeCell ref="J62:K62"/>
-    <mergeCell ref="K29:K30"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -35823,25 +35805,25 @@
       <c r="Q6" s="586"/>
     </row>
     <row r="7" spans="1:17" ht="42" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1025" t="s">
+      <c r="A7" s="1014" t="s">
         <v>173</v>
       </c>
-      <c r="B7" s="1025"/>
-      <c r="C7" s="1025"/>
-      <c r="D7" s="1025"/>
-      <c r="E7" s="1025"/>
-      <c r="F7" s="1025"/>
-      <c r="G7" s="1025"/>
-      <c r="H7" s="1025"/>
-      <c r="I7" s="1025"/>
-      <c r="J7" s="1025"/>
-      <c r="K7" s="1025"/>
-      <c r="L7" s="1025"/>
-      <c r="M7" s="1025"/>
-      <c r="N7" s="1025"/>
-      <c r="O7" s="1025"/>
-      <c r="P7" s="1025"/>
-      <c r="Q7" s="1025"/>
+      <c r="B7" s="1014"/>
+      <c r="C7" s="1014"/>
+      <c r="D7" s="1014"/>
+      <c r="E7" s="1014"/>
+      <c r="F7" s="1014"/>
+      <c r="G7" s="1014"/>
+      <c r="H7" s="1014"/>
+      <c r="I7" s="1014"/>
+      <c r="J7" s="1014"/>
+      <c r="K7" s="1014"/>
+      <c r="L7" s="1014"/>
+      <c r="M7" s="1014"/>
+      <c r="N7" s="1014"/>
+      <c r="O7" s="1014"/>
+      <c r="P7" s="1014"/>
+      <c r="Q7" s="1014"/>
     </row>
     <row r="8" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="593" t="s">
@@ -35921,11 +35903,11 @@
       <c r="L10" s="591" t="s">
         <v>177</v>
       </c>
-      <c r="O10" s="1034">
+      <c r="O10" s="1035">
         <f>+Datos!N10</f>
         <v>41951</v>
       </c>
-      <c r="P10" s="1034"/>
+      <c r="P10" s="1035"/>
       <c r="Q10" s="273"/>
     </row>
     <row r="11" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -36349,24 +36331,24 @@
       </c>
     </row>
     <row r="33" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1036" t="s">
+      <c r="A33" s="1037" t="s">
         <v>189</v>
       </c>
-      <c r="B33" s="1037"/>
-      <c r="C33" s="1037"/>
-      <c r="D33" s="1037"/>
-      <c r="E33" s="1037"/>
-      <c r="F33" s="1037"/>
-      <c r="G33" s="1037"/>
-      <c r="H33" s="1037"/>
-      <c r="I33" s="1037"/>
-      <c r="J33" s="1037"/>
-      <c r="K33" s="1037"/>
-      <c r="L33" s="1037"/>
-      <c r="M33" s="1037"/>
-      <c r="N33" s="1037"/>
-      <c r="O33" s="1037"/>
-      <c r="P33" s="1037"/>
+      <c r="B33" s="1038"/>
+      <c r="C33" s="1038"/>
+      <c r="D33" s="1038"/>
+      <c r="E33" s="1038"/>
+      <c r="F33" s="1038"/>
+      <c r="G33" s="1038"/>
+      <c r="H33" s="1038"/>
+      <c r="I33" s="1038"/>
+      <c r="J33" s="1038"/>
+      <c r="K33" s="1038"/>
+      <c r="L33" s="1038"/>
+      <c r="M33" s="1038"/>
+      <c r="N33" s="1038"/>
+      <c r="O33" s="1038"/>
+      <c r="P33" s="1038"/>
       <c r="Q33" s="600"/>
     </row>
     <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36400,11 +36382,11 @@
       <c r="M35" s="275" t="s">
         <v>191</v>
       </c>
-      <c r="N35" s="1035">
+      <c r="N35" s="1036">
         <f>+N34*0.95</f>
         <v>2.1669499999999999</v>
       </c>
-      <c r="O35" s="1035"/>
+      <c r="O35" s="1036"/>
       <c r="Q35" s="600"/>
     </row>
     <row r="36" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -36581,25 +36563,25 @@
       <c r="I55" s="454"/>
     </row>
     <row r="56" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="1026" t="s">
+      <c r="A56" s="1015" t="s">
         <v>159</v>
       </c>
-      <c r="B56" s="1026"/>
-      <c r="C56" s="1026"/>
-      <c r="D56" s="1026"/>
-      <c r="E56" s="1026"/>
-      <c r="F56" s="1026"/>
-      <c r="G56" s="1026"/>
-      <c r="H56" s="1026"/>
-      <c r="I56" s="1026"/>
-      <c r="J56" s="1026"/>
-      <c r="K56" s="1026"/>
-      <c r="L56" s="1026"/>
-      <c r="M56" s="1026"/>
-      <c r="N56" s="1026"/>
-      <c r="O56" s="1026"/>
-      <c r="P56" s="1026"/>
-      <c r="Q56" s="1026"/>
+      <c r="B56" s="1015"/>
+      <c r="C56" s="1015"/>
+      <c r="D56" s="1015"/>
+      <c r="E56" s="1015"/>
+      <c r="F56" s="1015"/>
+      <c r="G56" s="1015"/>
+      <c r="H56" s="1015"/>
+      <c r="I56" s="1015"/>
+      <c r="J56" s="1015"/>
+      <c r="K56" s="1015"/>
+      <c r="L56" s="1015"/>
+      <c r="M56" s="1015"/>
+      <c r="N56" s="1015"/>
+      <c r="O56" s="1015"/>
+      <c r="P56" s="1015"/>
+      <c r="Q56" s="1015"/>
     </row>
     <row r="58" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="224"/>
@@ -36673,7 +36655,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1040" t="s">
+      <c r="A2" s="1041" t="s">
         <v>151</v>
       </c>
       <c r="B2" s="114" t="s">
@@ -36687,7 +36669,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1041"/>
+      <c r="A3" s="1042"/>
       <c r="B3" s="245" t="s">
         <v>198</v>
       </c>
@@ -37135,18 +37117,18 @@
     </row>
     <row r="33" spans="1:8" ht="10.8" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="1038" t="s">
+      <c r="A34" s="1039" t="s">
         <v>201</v>
       </c>
-      <c r="B34" s="1039"/>
-      <c r="D34" s="1038" t="s">
+      <c r="B34" s="1040"/>
+      <c r="D34" s="1039" t="s">
         <v>202</v>
       </c>
-      <c r="E34" s="1039"/>
-      <c r="G34" s="1038" t="s">
+      <c r="E34" s="1040"/>
+      <c r="G34" s="1039" t="s">
         <v>203</v>
       </c>
-      <c r="H34" s="1039"/>
+      <c r="H34" s="1040"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="444">
@@ -37224,18 +37206,18 @@
     </row>
     <row r="38" spans="1:8" ht="10.8" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="1038" t="s">
+      <c r="A39" s="1039" t="s">
         <v>201</v>
       </c>
-      <c r="B39" s="1039"/>
-      <c r="D39" s="1038" t="s">
+      <c r="B39" s="1040"/>
+      <c r="D39" s="1039" t="s">
         <v>202</v>
       </c>
-      <c r="E39" s="1039"/>
-      <c r="G39" s="1038" t="s">
+      <c r="E39" s="1040"/>
+      <c r="G39" s="1039" t="s">
         <v>203</v>
       </c>
-      <c r="H39" s="1039"/>
+      <c r="H39" s="1040"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="444">
@@ -37381,10 +37363,10 @@
     <row r="3" spans="1:16" s="144" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="651"/>
       <c r="B3" s="477"/>
-      <c r="F3" s="1042"/>
-      <c r="G3" s="1042"/>
-      <c r="H3" s="1042"/>
-      <c r="I3" s="1042"/>
+      <c r="F3" s="1053"/>
+      <c r="G3" s="1053"/>
+      <c r="H3" s="1053"/>
+      <c r="I3" s="1053"/>
       <c r="J3" s="478"/>
       <c r="K3" s="478"/>
       <c r="L3" s="218"/>
@@ -37415,33 +37397,33 @@
     </row>
     <row r="6" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="652"/>
-      <c r="B6" s="1043"/>
-      <c r="C6" s="1043"/>
-      <c r="D6" s="1043"/>
-      <c r="E6" s="1043"/>
-      <c r="F6" s="1043"/>
-      <c r="G6" s="1043"/>
-      <c r="H6" s="1043"/>
-      <c r="I6" s="1043"/>
-      <c r="J6" s="1043"/>
-      <c r="K6" s="1043"/>
+      <c r="B6" s="1054"/>
+      <c r="C6" s="1054"/>
+      <c r="D6" s="1054"/>
+      <c r="E6" s="1054"/>
+      <c r="F6" s="1054"/>
+      <c r="G6" s="1054"/>
+      <c r="H6" s="1054"/>
+      <c r="I6" s="1054"/>
+      <c r="J6" s="1054"/>
+      <c r="K6" s="1054"/>
       <c r="L6" s="657"/>
     </row>
     <row r="7" spans="1:16" ht="42" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1046" t="s">
+      <c r="A7" s="1057" t="s">
         <v>204</v>
       </c>
-      <c r="B7" s="1047"/>
-      <c r="C7" s="1047"/>
-      <c r="D7" s="1047"/>
-      <c r="E7" s="1047"/>
-      <c r="F7" s="1047"/>
-      <c r="G7" s="1047"/>
-      <c r="H7" s="1047"/>
-      <c r="I7" s="1047"/>
-      <c r="J7" s="1047"/>
-      <c r="K7" s="1047"/>
-      <c r="L7" s="1048"/>
+      <c r="B7" s="1058"/>
+      <c r="C7" s="1058"/>
+      <c r="D7" s="1058"/>
+      <c r="E7" s="1058"/>
+      <c r="F7" s="1058"/>
+      <c r="G7" s="1058"/>
+      <c r="H7" s="1058"/>
+      <c r="I7" s="1058"/>
+      <c r="J7" s="1058"/>
+      <c r="K7" s="1058"/>
+      <c r="L7" s="1059"/>
       <c r="M7" s="553"/>
       <c r="N7" s="553"/>
       <c r="O7" s="553"/>
@@ -37598,13 +37580,13 @@
       <c r="C15" s="660"/>
       <c r="D15" s="661"/>
       <c r="E15" s="662"/>
-      <c r="F15" s="1051" t="s">
+      <c r="F15" s="1062" t="s">
         <v>213</v>
       </c>
-      <c r="G15" s="1052"/>
-      <c r="H15" s="1052"/>
-      <c r="I15" s="1052"/>
-      <c r="J15" s="1053"/>
+      <c r="G15" s="1063"/>
+      <c r="H15" s="1063"/>
+      <c r="I15" s="1063"/>
+      <c r="J15" s="1064"/>
       <c r="K15" s="663" t="s">
         <v>214</v>
       </c>
@@ -37625,10 +37607,10 @@
       <c r="H16" s="555">
         <v>3</v>
       </c>
-      <c r="I16" s="1049">
+      <c r="I16" s="1060">
         <v>4</v>
       </c>
-      <c r="J16" s="1050"/>
+      <c r="J16" s="1061"/>
       <c r="K16" s="665"/>
       <c r="L16" s="773"/>
     </row>
@@ -37654,8 +37636,8 @@
         <f>+G17</f>
         <v>4.76</v>
       </c>
-      <c r="I17" s="1054"/>
-      <c r="J17" s="1055"/>
+      <c r="I17" s="1065"/>
+      <c r="J17" s="1066"/>
       <c r="K17" s="667"/>
       <c r="L17" s="773"/>
     </row>
@@ -37680,8 +37662,8 @@
         <f>+F18+0.003</f>
         <v>0.4543888888888889</v>
       </c>
-      <c r="I18" s="1044"/>
-      <c r="J18" s="1045"/>
+      <c r="I18" s="1055"/>
+      <c r="J18" s="1056"/>
       <c r="K18" s="667"/>
       <c r="L18" s="773"/>
     </row>
@@ -37705,8 +37687,8 @@
         <f>+H18+$E$18</f>
         <v>0.46133333333333332</v>
       </c>
-      <c r="I19" s="1044"/>
-      <c r="J19" s="1045"/>
+      <c r="I19" s="1055"/>
+      <c r="J19" s="1056"/>
       <c r="K19" s="667"/>
       <c r="L19" s="773"/>
     </row>
@@ -37732,8 +37714,8 @@
         <f>+H19+$E$20</f>
         <v>0.4627222222222222</v>
       </c>
-      <c r="I20" s="1044"/>
-      <c r="J20" s="1045"/>
+      <c r="I20" s="1055"/>
+      <c r="J20" s="1056"/>
       <c r="K20" s="667"/>
       <c r="L20" s="773"/>
     </row>
@@ -37757,8 +37739,8 @@
         <f>+H20+$B$26</f>
         <v>0.4766111111111111</v>
       </c>
-      <c r="I21" s="1056"/>
-      <c r="J21" s="1057"/>
+      <c r="I21" s="1043"/>
+      <c r="J21" s="1044"/>
       <c r="K21" s="667"/>
       <c r="L21" s="773"/>
     </row>
@@ -37781,8 +37763,8 @@
       <c r="H22" s="556">
         <v>9.41</v>
       </c>
-      <c r="I22" s="1062"/>
-      <c r="J22" s="1063"/>
+      <c r="I22" s="1049"/>
+      <c r="J22" s="1050"/>
       <c r="K22" s="667"/>
       <c r="L22" s="773"/>
     </row>
@@ -37805,8 +37787,8 @@
       <c r="H23" s="556">
         <v>3.52</v>
       </c>
-      <c r="I23" s="1062"/>
-      <c r="J23" s="1063"/>
+      <c r="I23" s="1049"/>
+      <c r="J23" s="1050"/>
       <c r="K23" s="667"/>
       <c r="L23" s="773"/>
     </row>
@@ -37832,8 +37814,8 @@
         <f>+H23/H22*100</f>
         <v>37.40701381509033</v>
       </c>
-      <c r="I24" s="1064"/>
-      <c r="J24" s="1065"/>
+      <c r="I24" s="1051"/>
+      <c r="J24" s="1052"/>
       <c r="K24" s="668">
         <f>AVERAGE(F24:H24)</f>
         <v>37.389466930349265</v>
@@ -37849,8 +37831,8 @@
       <c r="F25" s="672"/>
       <c r="G25" s="672"/>
       <c r="H25" s="672"/>
-      <c r="I25" s="1061"/>
-      <c r="J25" s="1061"/>
+      <c r="I25" s="1048"/>
+      <c r="J25" s="1048"/>
       <c r="K25" s="673"/>
       <c r="L25" s="773"/>
     </row>
@@ -37877,9 +37859,9 @@
       <c r="G27" s="167"/>
       <c r="H27" s="167"/>
       <c r="I27" s="167"/>
-      <c r="J27" s="1058"/>
-      <c r="K27" s="1006"/>
-      <c r="L27" s="1059"/>
+      <c r="J27" s="1045"/>
+      <c r="K27" s="1007"/>
+      <c r="L27" s="1046"/>
     </row>
     <row r="28" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="674"/>
@@ -37902,9 +37884,9 @@
       <c r="G29" s="557"/>
       <c r="H29" s="557"/>
       <c r="I29" s="557"/>
-      <c r="J29" s="1058"/>
-      <c r="K29" s="1006"/>
-      <c r="L29" s="1059"/>
+      <c r="J29" s="1045"/>
+      <c r="K29" s="1007"/>
+      <c r="L29" s="1046"/>
     </row>
     <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="674"/>
@@ -37969,20 +37951,20 @@
     </row>
     <row r="46" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="47" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="1060" t="s">
+      <c r="A47" s="1047" t="s">
         <v>159</v>
       </c>
-      <c r="B47" s="1060"/>
-      <c r="C47" s="1060"/>
-      <c r="D47" s="1060"/>
-      <c r="E47" s="1060"/>
-      <c r="F47" s="1060"/>
-      <c r="G47" s="1060"/>
-      <c r="H47" s="1060"/>
-      <c r="I47" s="1060"/>
-      <c r="J47" s="1060"/>
-      <c r="K47" s="1060"/>
-      <c r="L47" s="1060"/>
+      <c r="B47" s="1047"/>
+      <c r="C47" s="1047"/>
+      <c r="D47" s="1047"/>
+      <c r="E47" s="1047"/>
+      <c r="F47" s="1047"/>
+      <c r="G47" s="1047"/>
+      <c r="H47" s="1047"/>
+      <c r="I47" s="1047"/>
+      <c r="J47" s="1047"/>
+      <c r="K47" s="1047"/>
+      <c r="L47" s="1047"/>
     </row>
   </sheetData>
   <protectedRanges>
@@ -37991,14 +37973,6 @@
     <protectedRange sqref="H12" name="Rango3_3_1_1_1_1"/>
   </protectedRanges>
   <mergeCells count="17">
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="J29:L29"/>
-    <mergeCell ref="A47:L47"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="J27:L27"/>
     <mergeCell ref="F3:I3"/>
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="I18:J18"/>
@@ -38008,6 +37982,14 @@
     <mergeCell ref="I16:J16"/>
     <mergeCell ref="F15:J15"/>
     <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="J29:L29"/>
+    <mergeCell ref="A47:L47"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="J27:L27"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -38113,16 +38095,16 @@
       <c r="K6" s="699"/>
     </row>
     <row r="7" spans="1:15" ht="42" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1069" t="s">
+      <c r="A7" s="1077" t="s">
         <v>225</v>
       </c>
-      <c r="B7" s="1070"/>
-      <c r="C7" s="1070"/>
-      <c r="D7" s="1070"/>
-      <c r="E7" s="1070"/>
-      <c r="F7" s="1070"/>
-      <c r="G7" s="1070"/>
-      <c r="H7" s="1071"/>
+      <c r="B7" s="1078"/>
+      <c r="C7" s="1078"/>
+      <c r="D7" s="1078"/>
+      <c r="E7" s="1078"/>
+      <c r="F7" s="1078"/>
+      <c r="G7" s="1078"/>
+      <c r="H7" s="1079"/>
       <c r="I7" s="700"/>
       <c r="J7" s="700"/>
       <c r="K7" s="700"/>
@@ -38267,139 +38249,139 @@
       <c r="H15" s="782"/>
     </row>
     <row r="16" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1072" t="s">
+      <c r="A16" s="1080" t="s">
         <v>227</v>
       </c>
-      <c r="B16" s="1073"/>
-      <c r="C16" s="1074"/>
-      <c r="D16" s="1066" t="s">
+      <c r="B16" s="1081"/>
+      <c r="C16" s="1082"/>
+      <c r="D16" s="1070" t="s">
         <v>228</v>
       </c>
-      <c r="E16" s="1078"/>
-      <c r="F16" s="1078"/>
-      <c r="G16" s="1078"/>
-      <c r="H16" s="1067"/>
+      <c r="E16" s="1086"/>
+      <c r="F16" s="1086"/>
+      <c r="G16" s="1086"/>
+      <c r="H16" s="1071"/>
     </row>
     <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1075"/>
-      <c r="B17" s="1076"/>
-      <c r="C17" s="1077"/>
+      <c r="A17" s="1083"/>
+      <c r="B17" s="1084"/>
+      <c r="C17" s="1085"/>
       <c r="D17" s="705" t="s">
         <v>229</v>
       </c>
       <c r="E17" s="706" t="s">
         <v>230</v>
       </c>
-      <c r="F17" s="1066" t="s">
+      <c r="F17" s="1070" t="s">
         <v>231</v>
       </c>
-      <c r="G17" s="1067"/>
+      <c r="G17" s="1071"/>
       <c r="H17" s="706" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1068" t="s">
+      <c r="A18" s="1072" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="1068"/>
-      <c r="C18" s="1068"/>
+      <c r="B18" s="1072"/>
+      <c r="C18" s="1072"/>
       <c r="D18" s="707"/>
       <c r="E18" s="708"/>
-      <c r="F18" s="1066"/>
-      <c r="G18" s="1067"/>
+      <c r="F18" s="1070"/>
+      <c r="G18" s="1071"/>
       <c r="H18" s="709"/>
     </row>
     <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1068" t="s">
+      <c r="A19" s="1072" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="1068"/>
-      <c r="C19" s="1068"/>
+      <c r="B19" s="1072"/>
+      <c r="C19" s="1072"/>
       <c r="D19" s="710">
         <v>1252.0999999999999</v>
       </c>
       <c r="E19" s="708"/>
-      <c r="F19" s="1066"/>
-      <c r="G19" s="1067"/>
+      <c r="F19" s="1070"/>
+      <c r="G19" s="1071"/>
       <c r="H19" s="709"/>
     </row>
     <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1068" t="s">
+      <c r="A20" s="1072" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="1068"/>
-      <c r="C20" s="1068"/>
+      <c r="B20" s="1072"/>
+      <c r="C20" s="1072"/>
       <c r="D20" s="710">
         <v>1253.5999999999999</v>
       </c>
       <c r="E20" s="708"/>
-      <c r="F20" s="1066"/>
-      <c r="G20" s="1067"/>
+      <c r="F20" s="1070"/>
+      <c r="G20" s="1071"/>
       <c r="H20" s="709"/>
     </row>
     <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1068" t="s">
+      <c r="A21" s="1072" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="1068"/>
-      <c r="C21" s="1068"/>
+      <c r="B21" s="1072"/>
+      <c r="C21" s="1072"/>
       <c r="D21" s="710">
         <v>1251.3</v>
       </c>
       <c r="E21" s="711">
         <v>2500.1</v>
       </c>
-      <c r="F21" s="1066"/>
-      <c r="G21" s="1067"/>
+      <c r="F21" s="1070"/>
+      <c r="G21" s="1071"/>
       <c r="H21" s="709"/>
     </row>
     <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1068" t="s">
+      <c r="A22" s="1072" t="s">
         <v>62</v>
       </c>
-      <c r="B22" s="1068"/>
-      <c r="C22" s="1068"/>
+      <c r="B22" s="1072"/>
+      <c r="C22" s="1072"/>
       <c r="D22" s="710">
         <v>1250.5999999999999</v>
       </c>
       <c r="E22" s="711">
         <v>2500.9</v>
       </c>
-      <c r="F22" s="1066"/>
-      <c r="G22" s="1067"/>
+      <c r="F22" s="1070"/>
+      <c r="G22" s="1071"/>
       <c r="H22" s="709"/>
     </row>
     <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1068" t="s">
+      <c r="A23" s="1072" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="1068"/>
-      <c r="C23" s="1068"/>
+      <c r="B23" s="1072"/>
+      <c r="C23" s="1072"/>
       <c r="D23" s="712"/>
       <c r="E23" s="711"/>
-      <c r="F23" s="1066"/>
-      <c r="G23" s="1067"/>
+      <c r="F23" s="1070"/>
+      <c r="G23" s="1071"/>
       <c r="H23" s="709"/>
     </row>
     <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1068" t="s">
+      <c r="A24" s="1072" t="s">
         <v>233</v>
       </c>
-      <c r="B24" s="1068"/>
-      <c r="C24" s="1068"/>
+      <c r="B24" s="1072"/>
+      <c r="C24" s="1072"/>
       <c r="D24" s="712"/>
       <c r="E24" s="711"/>
-      <c r="F24" s="1066"/>
-      <c r="G24" s="1067"/>
+      <c r="F24" s="1070"/>
+      <c r="G24" s="1071"/>
       <c r="H24" s="709"/>
     </row>
     <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1068" t="s">
+      <c r="A25" s="1072" t="s">
         <v>234</v>
       </c>
-      <c r="B25" s="1068"/>
-      <c r="C25" s="1068"/>
+      <c r="B25" s="1072"/>
+      <c r="C25" s="1072"/>
       <c r="D25" s="713">
         <f>SUM(D19+D20+D21+D22)</f>
         <v>5007.6000000000004</v>
@@ -38408,32 +38390,32 @@
         <f>SUM(E21:E24)</f>
         <v>5001</v>
       </c>
-      <c r="F25" s="1066"/>
-      <c r="G25" s="1067"/>
+      <c r="F25" s="1070"/>
+      <c r="G25" s="1071"/>
       <c r="H25" s="715"/>
     </row>
     <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1080" t="s">
+      <c r="A26" s="1067" t="s">
         <v>235</v>
       </c>
-      <c r="B26" s="1081"/>
-      <c r="C26" s="1082"/>
+      <c r="B26" s="1068"/>
+      <c r="C26" s="1069"/>
       <c r="D26" s="716">
         <v>3629.6</v>
       </c>
       <c r="E26" s="717">
         <v>4238.3999999999996</v>
       </c>
-      <c r="F26" s="1066"/>
-      <c r="G26" s="1067"/>
+      <c r="F26" s="1070"/>
+      <c r="G26" s="1071"/>
       <c r="H26" s="718"/>
     </row>
     <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1080" t="s">
+      <c r="A27" s="1067" t="s">
         <v>236</v>
       </c>
-      <c r="B27" s="1081"/>
-      <c r="C27" s="1082"/>
+      <c r="B27" s="1068"/>
+      <c r="C27" s="1069"/>
       <c r="D27" s="719">
         <f>+D25-D26</f>
         <v>1378.0000000000005</v>
@@ -38441,46 +38423,46 @@
       <c r="E27" s="714">
         <v>699.3</v>
       </c>
-      <c r="F27" s="1066"/>
-      <c r="G27" s="1067"/>
+      <c r="F27" s="1070"/>
+      <c r="G27" s="1071"/>
       <c r="H27" s="715"/>
     </row>
     <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1083" t="s">
+      <c r="A28" s="1074" t="s">
         <v>237</v>
       </c>
-      <c r="B28" s="1084"/>
-      <c r="C28" s="1085"/>
+      <c r="B28" s="1075"/>
+      <c r="C28" s="1076"/>
       <c r="D28" s="718">
         <v>12</v>
       </c>
       <c r="E28" s="717">
         <v>11</v>
       </c>
-      <c r="F28" s="1066"/>
-      <c r="G28" s="1067"/>
+      <c r="F28" s="1070"/>
+      <c r="G28" s="1071"/>
       <c r="H28" s="718"/>
     </row>
     <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1080" t="s">
+      <c r="A29" s="1067" t="s">
         <v>238</v>
       </c>
-      <c r="B29" s="1081"/>
-      <c r="C29" s="1082"/>
+      <c r="B29" s="1068"/>
+      <c r="C29" s="1069"/>
       <c r="D29" s="707"/>
       <c r="E29" s="711">
         <v>4620</v>
       </c>
-      <c r="F29" s="1066"/>
-      <c r="G29" s="1067"/>
+      <c r="F29" s="1070"/>
+      <c r="G29" s="1071"/>
       <c r="H29" s="707"/>
     </row>
     <row r="30" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1080" t="s">
+      <c r="A30" s="1067" t="s">
         <v>239</v>
       </c>
-      <c r="B30" s="1081"/>
-      <c r="C30" s="1082"/>
+      <c r="B30" s="1068"/>
+      <c r="C30" s="1069"/>
       <c r="D30" s="720">
         <f>(D27/D25*100)/100</f>
         <v>0.27518172377985467</v>
@@ -38489,8 +38471,8 @@
         <f>E27/E25*100</f>
         <v>13.983203359328133</v>
       </c>
-      <c r="F30" s="1066"/>
-      <c r="G30" s="1067"/>
+      <c r="F30" s="1070"/>
+      <c r="G30" s="1071"/>
       <c r="H30" s="722"/>
     </row>
     <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -38617,16 +38599,16 @@
     </row>
     <row r="43" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="45" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="1079" t="s">
+      <c r="A45" s="1073" t="s">
         <v>159</v>
       </c>
-      <c r="B45" s="1079"/>
-      <c r="C45" s="1079"/>
-      <c r="D45" s="1079"/>
-      <c r="E45" s="1079"/>
-      <c r="F45" s="1079"/>
-      <c r="G45" s="1079"/>
-      <c r="H45" s="1079"/>
+      <c r="B45" s="1073"/>
+      <c r="C45" s="1073"/>
+      <c r="D45" s="1073"/>
+      <c r="E45" s="1073"/>
+      <c r="F45" s="1073"/>
+      <c r="G45" s="1073"/>
+      <c r="H45" s="1073"/>
     </row>
   </sheetData>
   <protectedRanges>
@@ -38634,13 +38616,14 @@
     <protectedRange sqref="F12" name="Rango3_3_1_1_1_2"/>
   </protectedRanges>
   <mergeCells count="31">
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A16:C17"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
     <mergeCell ref="A45:H45"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A21:C21"/>
@@ -38657,14 +38640,13 @@
     <mergeCell ref="F29:G29"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="A25:C25"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A16:C17"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A20:C20"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.78740157480314965" right="0.78740157480314965" top="0.59055118110236227" bottom="0.39370078740157483" header="0" footer="0.39370078740157483"/>
@@ -38717,10 +38699,10 @@
     </row>
     <row r="3" spans="1:14" s="144" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="477"/>
-      <c r="E3" s="1042"/>
-      <c r="F3" s="1042"/>
-      <c r="G3" s="1042"/>
-      <c r="H3" s="1042"/>
+      <c r="E3" s="1053"/>
+      <c r="F3" s="1053"/>
+      <c r="G3" s="1053"/>
+      <c r="H3" s="1053"/>
       <c r="I3" s="478"/>
       <c r="J3" s="478"/>
       <c r="L3" s="478"/>
@@ -38762,17 +38744,17 @@
       <c r="J6" s="490"/>
     </row>
     <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="1088" t="s">
+      <c r="A7" s="1089" t="s">
         <v>242</v>
       </c>
-      <c r="B7" s="1088"/>
-      <c r="C7" s="1088"/>
-      <c r="D7" s="1088"/>
-      <c r="E7" s="1088"/>
-      <c r="F7" s="1088"/>
-      <c r="G7" s="1088"/>
-      <c r="H7" s="1088"/>
-      <c r="I7" s="1088"/>
+      <c r="B7" s="1089"/>
+      <c r="C7" s="1089"/>
+      <c r="D7" s="1089"/>
+      <c r="E7" s="1089"/>
+      <c r="F7" s="1089"/>
+      <c r="G7" s="1089"/>
+      <c r="H7" s="1089"/>
+      <c r="I7" s="1089"/>
       <c r="J7" s="491"/>
       <c r="K7" s="491"/>
       <c r="L7" s="491"/>
@@ -38780,17 +38762,17 @@
       <c r="N7" s="491"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="1089" t="s">
+      <c r="A8" s="1090" t="s">
         <v>243</v>
       </c>
-      <c r="B8" s="1089"/>
-      <c r="C8" s="1089"/>
-      <c r="D8" s="1089"/>
-      <c r="E8" s="1089"/>
-      <c r="F8" s="1089"/>
-      <c r="G8" s="1089"/>
-      <c r="H8" s="1089"/>
-      <c r="I8" s="1089"/>
+      <c r="B8" s="1090"/>
+      <c r="C8" s="1090"/>
+      <c r="D8" s="1090"/>
+      <c r="E8" s="1090"/>
+      <c r="F8" s="1090"/>
+      <c r="G8" s="1090"/>
+      <c r="H8" s="1090"/>
+      <c r="I8" s="1090"/>
       <c r="J8" s="492"/>
       <c r="K8" s="492"/>
       <c r="L8" s="492"/>
@@ -38799,17 +38781,17 @@
     </row>
     <row r="9" spans="1:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="1093" t="s">
+      <c r="A10" s="1094" t="s">
         <v>244</v>
       </c>
-      <c r="B10" s="1094"/>
-      <c r="C10" s="1094"/>
-      <c r="D10" s="1094"/>
-      <c r="E10" s="1094"/>
-      <c r="F10" s="1094"/>
-      <c r="G10" s="1094"/>
-      <c r="H10" s="1094"/>
-      <c r="I10" s="1095"/>
+      <c r="B10" s="1095"/>
+      <c r="C10" s="1095"/>
+      <c r="D10" s="1095"/>
+      <c r="E10" s="1095"/>
+      <c r="F10" s="1095"/>
+      <c r="G10" s="1095"/>
+      <c r="H10" s="1095"/>
+      <c r="I10" s="1096"/>
       <c r="J10" s="493"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -38900,17 +38882,17 @@
     </row>
     <row r="15" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="1090" t="s">
+      <c r="A16" s="1091" t="s">
         <v>254</v>
       </c>
-      <c r="B16" s="1091"/>
-      <c r="C16" s="1091"/>
-      <c r="D16" s="1091"/>
-      <c r="E16" s="1091"/>
-      <c r="F16" s="1091"/>
-      <c r="G16" s="1091"/>
-      <c r="H16" s="1091"/>
-      <c r="I16" s="1092"/>
+      <c r="B16" s="1092"/>
+      <c r="C16" s="1092"/>
+      <c r="D16" s="1092"/>
+      <c r="E16" s="1092"/>
+      <c r="F16" s="1092"/>
+      <c r="G16" s="1092"/>
+      <c r="H16" s="1092"/>
+      <c r="I16" s="1093"/>
       <c r="J16" s="493"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -38979,17 +38961,17 @@
       <c r="L20" s="388"/>
     </row>
     <row r="21" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1090" t="s">
+      <c r="A21" s="1091" t="s">
         <v>258</v>
       </c>
-      <c r="B21" s="1091"/>
-      <c r="C21" s="1091"/>
-      <c r="D21" s="1091"/>
-      <c r="E21" s="1091"/>
-      <c r="F21" s="1091"/>
-      <c r="G21" s="1091"/>
-      <c r="H21" s="1091"/>
-      <c r="I21" s="1092"/>
+      <c r="B21" s="1092"/>
+      <c r="C21" s="1092"/>
+      <c r="D21" s="1092"/>
+      <c r="E21" s="1092"/>
+      <c r="F21" s="1092"/>
+      <c r="G21" s="1092"/>
+      <c r="H21" s="1092"/>
+      <c r="I21" s="1093"/>
       <c r="J21" s="388"/>
       <c r="K21" s="388"/>
       <c r="L21" s="388"/>
@@ -39292,17 +39274,17 @@
       <c r="L35" s="388"/>
     </row>
     <row r="36" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1090" t="s">
+      <c r="A36" s="1091" t="s">
         <v>274</v>
       </c>
-      <c r="B36" s="1091"/>
-      <c r="C36" s="1091"/>
-      <c r="D36" s="1091"/>
-      <c r="E36" s="1091"/>
-      <c r="F36" s="1091"/>
-      <c r="G36" s="1091"/>
-      <c r="H36" s="1091"/>
-      <c r="I36" s="1092"/>
+      <c r="B36" s="1092"/>
+      <c r="C36" s="1092"/>
+      <c r="D36" s="1092"/>
+      <c r="E36" s="1092"/>
+      <c r="F36" s="1092"/>
+      <c r="G36" s="1092"/>
+      <c r="H36" s="1092"/>
+      <c r="I36" s="1093"/>
       <c r="J36" s="388"/>
       <c r="K36" s="388"/>
       <c r="L36" s="388"/>
@@ -39538,15 +39520,15 @@
       <c r="L48" s="388"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="1086"/>
-      <c r="B49" s="1086"/>
-      <c r="C49" s="1086"/>
-      <c r="D49" s="1086"/>
-      <c r="E49" s="1086"/>
-      <c r="F49" s="1087"/>
-      <c r="G49" s="1087"/>
-      <c r="H49" s="1087"/>
-      <c r="I49" s="1087"/>
+      <c r="A49" s="1087"/>
+      <c r="B49" s="1087"/>
+      <c r="C49" s="1087"/>
+      <c r="D49" s="1087"/>
+      <c r="E49" s="1087"/>
+      <c r="F49" s="1088"/>
+      <c r="G49" s="1088"/>
+      <c r="H49" s="1088"/>
+      <c r="I49" s="1088"/>
       <c r="J49" s="388"/>
       <c r="K49" s="388"/>
       <c r="L49" s="388"/>
